--- a/Data/ModelResponse/4_MAIA-like/evaluation/4_MAIA-like_evaluation_summary.xlsx
+++ b/Data/ModelResponse/4_MAIA-like/evaluation/4_MAIA-like_evaluation_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,102 +428,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -546,51 +531,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7894270833333333</v>
+        <v>15157</v>
       </c>
       <c r="G2" t="n">
         <v>0.7894270833333333</v>
       </c>
       <c r="H2" t="n">
-        <v>9554</v>
+        <v>0.7894270833333333</v>
       </c>
       <c r="I2" t="n">
-        <v>10369</v>
+        <v>0.7657440447487703</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7657440447487703</v>
+        <v>0.831065522294327</v>
       </c>
       <c r="K2" t="n">
-        <v>0.831065522294327</v>
+        <v>0.7970687145510215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7970687145510215</v>
+        <v>0.8172347412524062</v>
       </c>
       <c r="M2" t="n">
-        <v>9646</v>
+        <v>0.7481857764876633</v>
       </c>
       <c r="N2" t="n">
-        <v>8831</v>
+        <v>0.7811874222005736</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8172347412524062</v>
+        <v>7940</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7481857764876633</v>
+        <v>1614</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7811874222005736</v>
+        <v>2429</v>
       </c>
       <c r="R2" t="n">
-        <v>7940</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1614</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2429</v>
-      </c>
-      <c r="U2" t="n">
         <v>7217</v>
       </c>
     </row>
@@ -605,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,102 +592,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -734,51 +695,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.84375</v>
+        <v>675</v>
       </c>
       <c r="G2" t="n">
         <v>0.84375</v>
       </c>
       <c r="H2" t="n">
-        <v>387</v>
+        <v>0.84375</v>
       </c>
       <c r="I2" t="n">
-        <v>424</v>
+        <v>0.8089622641509434</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8089622641509434</v>
+        <v>0.8863049095607235</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8863049095607235</v>
+        <v>0.8458692971639951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8458692971639951</v>
+        <v>0.8829787234042553</v>
       </c>
       <c r="M2" t="n">
-        <v>413</v>
+        <v>0.8038740920096852</v>
       </c>
       <c r="N2" t="n">
-        <v>376</v>
+        <v>0.8415716096324461</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8829787234042553</v>
+        <v>343</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8038740920096852</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8415716096324461</v>
+        <v>81</v>
       </c>
       <c r="R2" t="n">
-        <v>343</v>
-      </c>
-      <c r="S2" t="n">
-        <v>44</v>
-      </c>
-      <c r="T2" t="n">
-        <v>81</v>
-      </c>
-      <c r="U2" t="n">
         <v>332</v>
       </c>
     </row>
@@ -801,51 +753,42 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.86625</v>
+        <v>693</v>
       </c>
       <c r="G3" t="n">
         <v>0.86625</v>
       </c>
       <c r="H3" t="n">
-        <v>404</v>
+        <v>0.86625</v>
       </c>
       <c r="I3" t="n">
-        <v>431</v>
+        <v>0.8445475638051044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8445475638051044</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.900990099009901</v>
+        <v>0.8718562874251498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8718562874251498</v>
+        <v>0.8915989159891599</v>
       </c>
       <c r="M3" t="n">
-        <v>396</v>
+        <v>0.8308080808080808</v>
       </c>
       <c r="N3" t="n">
-        <v>369</v>
+        <v>0.8601307189542483</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8915989159891599</v>
+        <v>364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8308080808080808</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8601307189542483</v>
+        <v>67</v>
       </c>
       <c r="R3" t="n">
-        <v>364</v>
-      </c>
-      <c r="S3" t="n">
-        <v>40</v>
-      </c>
-      <c r="T3" t="n">
-        <v>67</v>
-      </c>
-      <c r="U3" t="n">
         <v>329</v>
       </c>
     </row>
@@ -868,51 +811,42 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58125</v>
+        <v>930</v>
       </c>
       <c r="G4" t="n">
         <v>0.58125</v>
       </c>
       <c r="H4" t="n">
-        <v>821</v>
+        <v>0.58125</v>
       </c>
       <c r="I4" t="n">
-        <v>777</v>
+        <v>0.5971685971685972</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5971685971685972</v>
+        <v>0.5651644336175395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5651644336175395</v>
+        <v>0.5807259073842304</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5807259073842304</v>
+        <v>0.5662211421628189</v>
       </c>
       <c r="M4" t="n">
-        <v>779</v>
+        <v>0.5982028241335045</v>
       </c>
       <c r="N4" t="n">
-        <v>823</v>
+        <v>0.581772784019975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5662211421628189</v>
+        <v>464</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5982028241335045</v>
+        <v>357</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.581772784019975</v>
+        <v>313</v>
       </c>
       <c r="R4" t="n">
-        <v>464</v>
-      </c>
-      <c r="S4" t="n">
-        <v>357</v>
-      </c>
-      <c r="T4" t="n">
-        <v>313</v>
-      </c>
-      <c r="U4" t="n">
         <v>466</v>
       </c>
     </row>
@@ -935,51 +869,42 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7837499999999999</v>
+        <v>1254</v>
       </c>
       <c r="G5" t="n">
         <v>0.7837499999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>805</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>903</v>
+        <v>0.7541528239202658</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7541528239202658</v>
+        <v>0.8459627329192546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8459627329192546</v>
+        <v>0.797423887587822</v>
       </c>
       <c r="L5" t="n">
-        <v>0.797423887587822</v>
+        <v>0.8220946915351507</v>
       </c>
       <c r="M5" t="n">
-        <v>795</v>
+        <v>0.720754716981132</v>
       </c>
       <c r="N5" t="n">
-        <v>697</v>
+        <v>0.7680965147453083</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8220946915351507</v>
+        <v>681</v>
       </c>
       <c r="P5" t="n">
-        <v>0.720754716981132</v>
+        <v>124</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7680965147453083</v>
+        <v>222</v>
       </c>
       <c r="R5" t="n">
-        <v>681</v>
-      </c>
-      <c r="S5" t="n">
-        <v>124</v>
-      </c>
-      <c r="T5" t="n">
-        <v>222</v>
-      </c>
-      <c r="U5" t="n">
         <v>573</v>
       </c>
     </row>
@@ -1002,51 +927,42 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.834375</v>
+        <v>1335</v>
       </c>
       <c r="G6" t="n">
         <v>0.834375</v>
       </c>
       <c r="H6" t="n">
-        <v>821</v>
+        <v>0.834375</v>
       </c>
       <c r="I6" t="n">
-        <v>898</v>
+        <v>0.8095768374164811</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8095768374164811</v>
+        <v>0.8855054811205847</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8855054811205847</v>
+        <v>0.8458406050029087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8458406050029087</v>
+        <v>0.8660968660968661</v>
       </c>
       <c r="M6" t="n">
-        <v>779</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="N6" t="n">
-        <v>702</v>
+        <v>0.8210668467251857</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8660968660968661</v>
+        <v>727</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7804878048780488</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8210668467251857</v>
+        <v>171</v>
       </c>
       <c r="R6" t="n">
-        <v>727</v>
-      </c>
-      <c r="S6" t="n">
-        <v>94</v>
-      </c>
-      <c r="T6" t="n">
-        <v>171</v>
-      </c>
-      <c r="U6" t="n">
         <v>608</v>
       </c>
     </row>
@@ -1069,51 +985,42 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.91625</v>
+        <v>1466</v>
       </c>
       <c r="G7" t="n">
         <v>0.91625</v>
       </c>
       <c r="H7" t="n">
-        <v>740</v>
+        <v>0.91625</v>
       </c>
       <c r="I7" t="n">
-        <v>806</v>
+        <v>0.8759305210918115</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8759305210918115</v>
+        <v>0.9540540540540541</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9540540540540541</v>
+        <v>0.9133247089262613</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9133247089262613</v>
+        <v>0.9571788413098237</v>
       </c>
       <c r="M7" t="n">
-        <v>860</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="N7" t="n">
-        <v>794</v>
+        <v>0.9189842805320435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9571788413098237</v>
+        <v>706</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8837209302325582</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9189842805320435</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>706</v>
-      </c>
-      <c r="S7" t="n">
-        <v>34</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" t="n">
         <v>760</v>
       </c>
     </row>
@@ -1136,51 +1043,42 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.934375</v>
+        <v>1495</v>
       </c>
       <c r="G8" t="n">
         <v>0.934375</v>
       </c>
       <c r="H8" t="n">
-        <v>769</v>
+        <v>0.934375</v>
       </c>
       <c r="I8" t="n">
-        <v>794</v>
+        <v>0.9181360201511335</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9181360201511335</v>
+        <v>0.9479843953185956</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9479843953185956</v>
+        <v>0.9328214971209213</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9328214971209213</v>
+        <v>0.9503722084367245</v>
       </c>
       <c r="M8" t="n">
-        <v>831</v>
+        <v>0.9217809867629362</v>
       </c>
       <c r="N8" t="n">
-        <v>806</v>
+        <v>0.9358582773365912</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9503722084367245</v>
+        <v>729</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9217809867629362</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9358582773365912</v>
+        <v>65</v>
       </c>
       <c r="R8" t="n">
-        <v>729</v>
-      </c>
-      <c r="S8" t="n">
-        <v>40</v>
-      </c>
-      <c r="T8" t="n">
-        <v>65</v>
-      </c>
-      <c r="U8" t="n">
         <v>766</v>
       </c>
     </row>
@@ -1203,51 +1101,42 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.728125</v>
+        <v>1165</v>
       </c>
       <c r="G9" t="n">
         <v>0.728125</v>
       </c>
       <c r="H9" t="n">
-        <v>822</v>
+        <v>0.728125</v>
       </c>
       <c r="I9" t="n">
-        <v>997</v>
+        <v>0.6940822467402207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6940822467402207</v>
+        <v>0.8418491484184915</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8418491484184915</v>
+        <v>0.7608576140736668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7608576140736668</v>
+        <v>0.7844112769485904</v>
       </c>
       <c r="M9" t="n">
-        <v>778</v>
+        <v>0.6079691516709511</v>
       </c>
       <c r="N9" t="n">
-        <v>603</v>
+        <v>0.6850108616944243</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7844112769485904</v>
+        <v>692</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6079691516709511</v>
+        <v>130</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6850108616944243</v>
+        <v>305</v>
       </c>
       <c r="R9" t="n">
-        <v>692</v>
-      </c>
-      <c r="S9" t="n">
-        <v>130</v>
-      </c>
-      <c r="T9" t="n">
-        <v>305</v>
-      </c>
-      <c r="U9" t="n">
         <v>473</v>
       </c>
     </row>
@@ -1270,51 +1159,42 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.83375</v>
+        <v>1334</v>
       </c>
       <c r="G10" t="n">
         <v>0.83375</v>
       </c>
       <c r="H10" t="n">
-        <v>804</v>
+        <v>0.83375</v>
       </c>
       <c r="I10" t="n">
-        <v>946</v>
+        <v>0.7843551797040169</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7843551797040169</v>
+        <v>0.9228855721393034</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9228855721393034</v>
+        <v>0.848</v>
       </c>
       <c r="L10" t="n">
-        <v>0.848</v>
+        <v>0.9051987767584098</v>
       </c>
       <c r="M10" t="n">
-        <v>796</v>
+        <v>0.7437185929648241</v>
       </c>
       <c r="N10" t="n">
-        <v>654</v>
+        <v>0.8165517241379311</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9051987767584098</v>
+        <v>742</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7437185929648241</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8165517241379311</v>
+        <v>204</v>
       </c>
       <c r="R10" t="n">
-        <v>742</v>
-      </c>
-      <c r="S10" t="n">
-        <v>62</v>
-      </c>
-      <c r="T10" t="n">
-        <v>204</v>
-      </c>
-      <c r="U10" t="n">
         <v>592</v>
       </c>
     </row>
@@ -1337,51 +1217,42 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7006250000000001</v>
+        <v>1121</v>
       </c>
       <c r="G11" t="n">
         <v>0.7006250000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>812</v>
+        <v>0.7006250000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>727</v>
+        <v>0.7290233837689133</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7290233837689133</v>
+        <v>0.6527093596059114</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6527093596059114</v>
+        <v>0.6887589343729694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6887589343729694</v>
+        <v>0.6769759450171822</v>
       </c>
       <c r="M11" t="n">
-        <v>788</v>
+        <v>0.75</v>
       </c>
       <c r="N11" t="n">
-        <v>873</v>
+        <v>0.7116195063214931</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6769759450171822</v>
+        <v>530</v>
       </c>
       <c r="P11" t="n">
-        <v>0.75</v>
+        <v>282</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7116195063214931</v>
+        <v>197</v>
       </c>
       <c r="R11" t="n">
-        <v>530</v>
-      </c>
-      <c r="S11" t="n">
-        <v>282</v>
-      </c>
-      <c r="T11" t="n">
-        <v>197</v>
-      </c>
-      <c r="U11" t="n">
         <v>591</v>
       </c>
     </row>
@@ -1404,51 +1275,42 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.885625</v>
+        <v>1417</v>
       </c>
       <c r="G12" t="n">
         <v>0.885625</v>
       </c>
       <c r="H12" t="n">
-        <v>788</v>
+        <v>0.885625</v>
       </c>
       <c r="I12" t="n">
-        <v>781</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8873239436619719</v>
+        <v>0.8794416243654822</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8794416243654822</v>
+        <v>0.8833652007648184</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8833652007648184</v>
+        <v>0.884004884004884</v>
       </c>
       <c r="M12" t="n">
-        <v>812</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="N12" t="n">
-        <v>819</v>
+        <v>0.8877988963825875</v>
       </c>
       <c r="O12" t="n">
-        <v>0.884004884004884</v>
+        <v>693</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8916256157635468</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8877988963825875</v>
+        <v>88</v>
       </c>
       <c r="R12" t="n">
-        <v>693</v>
-      </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="n">
-        <v>88</v>
-      </c>
-      <c r="U12" t="n">
         <v>724</v>
       </c>
     </row>
@@ -1471,51 +1333,42 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.685625</v>
+        <v>1097</v>
       </c>
       <c r="G13" t="n">
         <v>0.685625</v>
       </c>
       <c r="H13" t="n">
-        <v>813</v>
+        <v>0.685625</v>
       </c>
       <c r="I13" t="n">
-        <v>968</v>
+        <v>0.6601239669421488</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6601239669421488</v>
+        <v>0.7859778597785978</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7859778597785978</v>
+        <v>0.7175743964065133</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7175743964065133</v>
+        <v>0.7246835443037974</v>
       </c>
       <c r="M13" t="n">
-        <v>787</v>
+        <v>0.5819567979669632</v>
       </c>
       <c r="N13" t="n">
-        <v>632</v>
+        <v>0.6455250176180409</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7246835443037974</v>
+        <v>639</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5819567979669632</v>
+        <v>174</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6455250176180409</v>
+        <v>329</v>
       </c>
       <c r="R13" t="n">
-        <v>639</v>
-      </c>
-      <c r="S13" t="n">
-        <v>174</v>
-      </c>
-      <c r="T13" t="n">
-        <v>329</v>
-      </c>
-      <c r="U13" t="n">
         <v>458</v>
       </c>
     </row>
@@ -1538,51 +1391,42 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.734375</v>
+        <v>1175</v>
       </c>
       <c r="G14" t="n">
         <v>0.734375</v>
       </c>
       <c r="H14" t="n">
-        <v>768</v>
+        <v>0.734375</v>
       </c>
       <c r="I14" t="n">
-        <v>917</v>
+        <v>0.6870229007633588</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6870229007633588</v>
+        <v>0.8203125</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8203125</v>
+        <v>0.7477744807121662</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7477744807121662</v>
+        <v>0.7979502196193266</v>
       </c>
       <c r="M14" t="n">
-        <v>832</v>
+        <v>0.6550480769230769</v>
       </c>
       <c r="N14" t="n">
-        <v>683</v>
+        <v>0.7194719471947193</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7979502196193266</v>
+        <v>630</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6550480769230769</v>
+        <v>138</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7194719471947193</v>
+        <v>287</v>
       </c>
       <c r="R14" t="n">
-        <v>630</v>
-      </c>
-      <c r="S14" t="n">
-        <v>138</v>
-      </c>
-      <c r="T14" t="n">
-        <v>287</v>
-      </c>
-      <c r="U14" t="n">
         <v>545</v>
       </c>
     </row>
@@ -1597,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U101"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,102 +1452,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -1726,51 +1555,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G2" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>89</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I2" t="n">
-        <v>89</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="J2" t="n">
         <v>0.8089887640449438</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.8089887640449437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8089887640449437</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="M2" t="n">
-        <v>103</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="N2" t="n">
-        <v>103</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8349514563106796</v>
+        <v>72</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8349514563106796</v>
+        <v>17</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8349514563106796</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>72</v>
-      </c>
-      <c r="S2" t="n">
-        <v>17</v>
-      </c>
-      <c r="T2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U2" t="n">
         <v>86</v>
       </c>
     </row>
@@ -1793,53 +1613,44 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G3" t="n">
         <v>0.78125</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>0.78125</v>
       </c>
       <c r="I3" t="n">
-        <v>99</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="J3" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7812499999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.7575757575757576</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.8064516129032258</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.7812499999999999</v>
       </c>
-      <c r="M3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N3" t="n">
-        <v>93</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.8064516129032258</v>
+        <v>75</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7575757575757576</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7812499999999999</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
         <v>75</v>
       </c>
-      <c r="S3" t="n">
-        <v>18</v>
-      </c>
-      <c r="T3" t="n">
-        <v>24</v>
-      </c>
-      <c r="U3" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1860,51 +1671,42 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G4" t="n">
         <v>0.828125</v>
       </c>
       <c r="H4" t="n">
-        <v>110</v>
+        <v>0.828125</v>
       </c>
       <c r="I4" t="n">
-        <v>115</v>
+        <v>0.8347826086956521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8347826086956521</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="M4" t="n">
-        <v>82</v>
+        <v>0.7682926829268293</v>
       </c>
       <c r="N4" t="n">
-        <v>77</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8181818181818182</v>
+        <v>96</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7682926829268293</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7924528301886793</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>96</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" t="n">
-        <v>19</v>
-      </c>
-      <c r="U4" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1927,51 +1729,42 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I5" t="n">
-        <v>124</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.865979381443299</v>
+        <v>0.7601809954751131</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7601809954751131</v>
+        <v>0.8088235294117647</v>
       </c>
       <c r="M5" t="n">
-        <v>95</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="N5" t="n">
-        <v>68</v>
+        <v>0.6748466257668712</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8088235294117647</v>
+        <v>84</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5789473684210527</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6748466257668712</v>
+        <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>84</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>40</v>
-      </c>
-      <c r="U5" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1994,51 +1787,42 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9010416666666666</v>
+        <v>173</v>
       </c>
       <c r="G6" t="n">
         <v>0.9010416666666666</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>0.9010416666666666</v>
       </c>
       <c r="I6" t="n">
-        <v>102</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.9029126213592233</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9029126213592233</v>
+        <v>0.9073170731707318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9073170731707318</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>0.8938547486033519</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8888888888888888</v>
+        <v>93</v>
       </c>
       <c r="P6" t="n">
-        <v>0.898876404494382</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8938547486033519</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>93</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>9</v>
-      </c>
-      <c r="U6" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2061,51 +1845,42 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7864583333333334</v>
+        <v>151</v>
       </c>
       <c r="G7" t="n">
         <v>0.7864583333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I7" t="n">
-        <v>109</v>
+        <v>0.7431192660550459</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7431192660550459</v>
+        <v>0.8617021276595744</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.7980295566502462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7980295566502462</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="M7" t="n">
-        <v>98</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N7" t="n">
-        <v>83</v>
+        <v>0.7734806629834255</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8433734939759037</v>
+        <v>81</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7142857142857143</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7734806629834255</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>81</v>
-      </c>
-      <c r="S7" t="n">
-        <v>13</v>
-      </c>
-      <c r="T7" t="n">
-        <v>28</v>
-      </c>
-      <c r="U7" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2128,51 +1903,42 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G8" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I8" t="n">
-        <v>106</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0.76</v>
       </c>
       <c r="N8" t="n">
-        <v>86</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8837209302325582</v>
+        <v>82</v>
       </c>
       <c r="P8" t="n">
-        <v>0.76</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8172043010752689</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>82</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U8" t="n">
         <v>76</v>
       </c>
     </row>
@@ -2195,51 +1961,42 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G9" t="n">
         <v>0.78125</v>
       </c>
       <c r="H9" t="n">
-        <v>104</v>
+        <v>0.78125</v>
       </c>
       <c r="I9" t="n">
-        <v>112</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7767857142857143</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8365384615384616</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7875</v>
       </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>0.7159090909090909</v>
       </c>
       <c r="N9" t="n">
-        <v>80</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7875</v>
+        <v>87</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7159090909090909</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7500000000000001</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>87</v>
-      </c>
-      <c r="S9" t="n">
-        <v>17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>25</v>
-      </c>
-      <c r="U9" t="n">
         <v>63</v>
       </c>
     </row>
@@ -2262,51 +2019,42 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6875</v>
+        <v>132</v>
       </c>
       <c r="G10" t="n">
         <v>0.6875</v>
       </c>
       <c r="H10" t="n">
-        <v>106</v>
+        <v>0.6875</v>
       </c>
       <c r="I10" t="n">
-        <v>136</v>
+        <v>0.6691176470588235</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6691176470588235</v>
+        <v>0.8584905660377359</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8584905660377359</v>
+        <v>0.7520661157024794</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7520661157024794</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="M10" t="n">
-        <v>86</v>
+        <v>0.4767441860465116</v>
       </c>
       <c r="N10" t="n">
-        <v>56</v>
+        <v>0.5774647887323943</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7321428571428571</v>
+        <v>91</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4767441860465116</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5774647887323943</v>
+        <v>45</v>
       </c>
       <c r="R10" t="n">
-        <v>91</v>
-      </c>
-      <c r="S10" t="n">
-        <v>15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>45</v>
-      </c>
-      <c r="U10" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2329,51 +2077,42 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I11" t="n">
-        <v>81</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7570621468926554</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7570621468926554</v>
+        <v>0.7387387387387387</v>
       </c>
       <c r="M11" t="n">
-        <v>96</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="N11" t="n">
-        <v>111</v>
+        <v>0.7922705314009663</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7387387387387387</v>
+        <v>67</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8541666666666666</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7922705314009663</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>67</v>
-      </c>
-      <c r="S11" t="n">
-        <v>29</v>
-      </c>
-      <c r="T11" t="n">
-        <v>14</v>
-      </c>
-      <c r="U11" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2396,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G12" t="n">
         <v>0.78125</v>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>0.78125</v>
       </c>
       <c r="I12" t="n">
-        <v>96</v>
+        <v>0.78125</v>
       </c>
       <c r="J12" t="n">
         <v>0.78125</v>
@@ -2417,32 +2156,23 @@
         <v>0.78125</v>
       </c>
       <c r="M12" t="n">
-        <v>96</v>
+        <v>0.78125</v>
       </c>
       <c r="N12" t="n">
-        <v>96</v>
+        <v>0.78125</v>
       </c>
       <c r="O12" t="n">
-        <v>0.78125</v>
+        <v>75</v>
       </c>
       <c r="P12" t="n">
-        <v>0.78125</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.78125</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
         <v>75</v>
       </c>
-      <c r="S12" t="n">
-        <v>21</v>
-      </c>
-      <c r="T12" t="n">
-        <v>21</v>
-      </c>
-      <c r="U12" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2463,51 +2193,42 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8177083333333334</v>
+        <v>157</v>
       </c>
       <c r="G13" t="n">
         <v>0.8177083333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>89</v>
+        <v>0.8426966292134831</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8426966292134831</v>
+        <v>0.78125</v>
       </c>
       <c r="K13" t="n">
-        <v>0.78125</v>
+        <v>0.8108108108108107</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8108108108108107</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="M13" t="n">
-        <v>96</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>103</v>
+        <v>0.8241206030150753</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7961165048543689</v>
+        <v>75</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8541666666666666</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8241206030150753</v>
+        <v>14</v>
       </c>
       <c r="R13" t="n">
-        <v>75</v>
-      </c>
-      <c r="S13" t="n">
-        <v>21</v>
-      </c>
-      <c r="T13" t="n">
-        <v>14</v>
-      </c>
-      <c r="U13" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2530,51 +2251,42 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G14" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I14" t="n">
-        <v>113</v>
+        <v>0.8053097345132744</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8053097345132744</v>
+        <v>0.8348623853211009</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8348623853211009</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8198198198198198</v>
+        <v>0.7721518987341772</v>
       </c>
       <c r="M14" t="n">
-        <v>83</v>
+        <v>0.7349397590361446</v>
       </c>
       <c r="N14" t="n">
-        <v>79</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7721518987341772</v>
+        <v>91</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7349397590361446</v>
+        <v>18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7530864197530864</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>91</v>
-      </c>
-      <c r="S14" t="n">
-        <v>18</v>
-      </c>
-      <c r="T14" t="n">
-        <v>22</v>
-      </c>
-      <c r="U14" t="n">
         <v>61</v>
       </c>
     </row>
@@ -2597,51 +2309,42 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G15" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I15" t="n">
-        <v>79</v>
+        <v>0.759493670886076</v>
       </c>
       <c r="J15" t="n">
-        <v>0.759493670886076</v>
+        <v>0.6382978723404256</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6382978723404256</v>
+        <v>0.6936416184971099</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6936416184971099</v>
+        <v>0.6991150442477876</v>
       </c>
       <c r="M15" t="n">
-        <v>98</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="N15" t="n">
-        <v>113</v>
+        <v>0.7488151658767771</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6991150442477876</v>
+        <v>60</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8061224489795918</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7488151658767771</v>
+        <v>19</v>
       </c>
       <c r="R15" t="n">
-        <v>60</v>
-      </c>
-      <c r="S15" t="n">
-        <v>34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>19</v>
-      </c>
-      <c r="U15" t="n">
         <v>79</v>
       </c>
     </row>
@@ -2664,51 +2367,42 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G16" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I16" t="n">
-        <v>127</v>
+        <v>0.6377952755905512</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6377952755905512</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9</v>
+        <v>0.7465437788018432</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7465437788018432</v>
+        <v>0.8615384615384616</v>
       </c>
       <c r="M16" t="n">
-        <v>102</v>
+        <v>0.5490196078431373</v>
       </c>
       <c r="N16" t="n">
-        <v>65</v>
+        <v>0.6706586826347305</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8615384615384616</v>
+        <v>81</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5490196078431373</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6706586826347305</v>
+        <v>46</v>
       </c>
       <c r="R16" t="n">
-        <v>81</v>
-      </c>
-      <c r="S16" t="n">
-        <v>9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>46</v>
-      </c>
-      <c r="U16" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2731,51 +2425,42 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.84375</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
         <v>0.84375</v>
       </c>
       <c r="H17" t="n">
-        <v>81</v>
+        <v>0.84375</v>
       </c>
       <c r="I17" t="n">
-        <v>75</v>
+        <v>0.84</v>
       </c>
       <c r="J17" t="n">
-        <v>0.84</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M17" t="n">
-        <v>111</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="N17" t="n">
-        <v>117</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8461538461538461</v>
+        <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8918918918918919</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.868421052631579</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>63</v>
-      </c>
-      <c r="S17" t="n">
-        <v>18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>12</v>
-      </c>
-      <c r="U17" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2798,51 +2483,42 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.734375</v>
+        <v>141</v>
       </c>
       <c r="G18" t="n">
         <v>0.734375</v>
       </c>
       <c r="H18" t="n">
-        <v>105</v>
+        <v>0.734375</v>
       </c>
       <c r="I18" t="n">
-        <v>88</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8068181818181818</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6761904761904762</v>
+        <v>0.7357512953367875</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7357512953367875</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="M18" t="n">
-        <v>87</v>
+        <v>0.8045977011494253</v>
       </c>
       <c r="N18" t="n">
-        <v>104</v>
+        <v>0.7329842931937174</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6730769230769231</v>
+        <v>71</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8045977011494253</v>
+        <v>34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7329842931937174</v>
+        <v>17</v>
       </c>
       <c r="R18" t="n">
-        <v>71</v>
-      </c>
-      <c r="S18" t="n">
-        <v>34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>17</v>
-      </c>
-      <c r="U18" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2865,51 +2541,42 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G19" t="n">
         <v>0.796875</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>0.796875</v>
       </c>
       <c r="I19" t="n">
-        <v>100</v>
+        <v>0.79</v>
       </c>
       <c r="J19" t="n">
-        <v>0.79</v>
+        <v>0.8144329896907216</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8144329896907216</v>
+        <v>0.802030456852792</v>
       </c>
       <c r="L19" t="n">
-        <v>0.802030456852792</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="M19" t="n">
-        <v>95</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="N19" t="n">
-        <v>92</v>
+        <v>0.7914438502673796</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8043478260869565</v>
+        <v>79</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7789473684210526</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7914438502673796</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>79</v>
-      </c>
-      <c r="S19" t="n">
-        <v>18</v>
-      </c>
-      <c r="T19" t="n">
-        <v>21</v>
-      </c>
-      <c r="U19" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2932,51 +2599,42 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G20" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>83</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I20" t="n">
-        <v>122</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="J20" t="n">
-        <v>0.639344262295082</v>
+        <v>0.9397590361445783</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.7609756097560976</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7609756097560976</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="M20" t="n">
-        <v>109</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="N20" t="n">
-        <v>70</v>
+        <v>0.7262569832402235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9285714285714286</v>
+        <v>78</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5963302752293578</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7262569832402235</v>
+        <v>44</v>
       </c>
       <c r="R20" t="n">
-        <v>78</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>44</v>
-      </c>
-      <c r="U20" t="n">
         <v>65</v>
       </c>
     </row>
@@ -2999,51 +2657,42 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G21" t="n">
         <v>0.796875</v>
       </c>
       <c r="H21" t="n">
-        <v>99</v>
+        <v>0.796875</v>
       </c>
       <c r="I21" t="n">
-        <v>114</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.8787878787878788</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8169014084507042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8169014084507042</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M21" t="n">
-        <v>93</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="N21" t="n">
-        <v>78</v>
+        <v>0.7719298245614036</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8461538461538461</v>
+        <v>87</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7096774193548387</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7719298245614036</v>
+        <v>27</v>
       </c>
       <c r="R21" t="n">
-        <v>87</v>
-      </c>
-      <c r="S21" t="n">
-        <v>12</v>
-      </c>
-      <c r="T21" t="n">
-        <v>27</v>
-      </c>
-      <c r="U21" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3066,51 +2715,42 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G22" t="n">
         <v>0.828125</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>0.828125</v>
       </c>
       <c r="I22" t="n">
-        <v>76</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7654320987654321</v>
+        <v>0.7898089171974522</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7898089171974522</v>
+        <v>0.8362068965517241</v>
       </c>
       <c r="M22" t="n">
-        <v>111</v>
+        <v>0.8738738738738738</v>
       </c>
       <c r="N22" t="n">
-        <v>116</v>
+        <v>0.8546255506607928</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8362068965517241</v>
+        <v>62</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8738738738738738</v>
+        <v>19</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8546255506607928</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>62</v>
-      </c>
-      <c r="S22" t="n">
-        <v>19</v>
-      </c>
-      <c r="T22" t="n">
-        <v>14</v>
-      </c>
-      <c r="U22" t="n">
         <v>97</v>
       </c>
     </row>
@@ -3133,51 +2773,42 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7552083333333334</v>
+        <v>145</v>
       </c>
       <c r="G23" t="n">
         <v>0.7552083333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>84</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I23" t="n">
-        <v>103</v>
+        <v>0.6796116504854369</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6796116504854369</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7486631016042781</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7486631016042781</v>
+        <v>0.8426966292134831</v>
       </c>
       <c r="M23" t="n">
-        <v>108</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="N23" t="n">
-        <v>89</v>
+        <v>0.7614213197969543</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8426966292134831</v>
+        <v>70</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6944444444444444</v>
+        <v>14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7614213197969543</v>
+        <v>33</v>
       </c>
       <c r="R23" t="n">
-        <v>70</v>
-      </c>
-      <c r="S23" t="n">
-        <v>14</v>
-      </c>
-      <c r="T23" t="n">
-        <v>33</v>
-      </c>
-      <c r="U23" t="n">
         <v>75</v>
       </c>
     </row>
@@ -3200,51 +2831,42 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8489583333333334</v>
+        <v>163</v>
       </c>
       <c r="G24" t="n">
         <v>0.8489583333333334</v>
       </c>
       <c r="H24" t="n">
-        <v>88</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="I24" t="n">
-        <v>87</v>
+        <v>0.8390804597701149</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8390804597701149</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.8342857142857142</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8342857142857142</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M24" t="n">
-        <v>104</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="N24" t="n">
-        <v>105</v>
+        <v>0.8612440191387559</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8571428571428571</v>
+        <v>73</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8653846153846154</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8612440191387559</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>73</v>
-      </c>
-      <c r="S24" t="n">
-        <v>15</v>
-      </c>
-      <c r="T24" t="n">
-        <v>14</v>
-      </c>
-      <c r="U24" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3267,51 +2889,42 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G25" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I25" t="n">
-        <v>98</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7817258883248731</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7817258883248731</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="M25" t="n">
-        <v>93</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>0.770053475935829</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7659574468085106</v>
+        <v>77</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7741935483870968</v>
+        <v>22</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.770053475935829</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
-        <v>77</v>
-      </c>
-      <c r="S25" t="n">
-        <v>22</v>
-      </c>
-      <c r="T25" t="n">
-        <v>21</v>
-      </c>
-      <c r="U25" t="n">
         <v>72</v>
       </c>
     </row>
@@ -3334,51 +2947,42 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8177083333333334</v>
+        <v>157</v>
       </c>
       <c r="G26" t="n">
         <v>0.8177083333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I26" t="n">
-        <v>110</v>
+        <v>0.7363636363636363</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7363636363636363</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.8223350253807107</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8223350253807107</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="M26" t="n">
-        <v>105</v>
+        <v>0.7238095238095238</v>
       </c>
       <c r="N26" t="n">
-        <v>82</v>
+        <v>0.8128342245989305</v>
       </c>
       <c r="O26" t="n">
-        <v>0.926829268292683</v>
+        <v>81</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7238095238095238</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8128342245989305</v>
+        <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>81</v>
-      </c>
-      <c r="S26" t="n">
-        <v>6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>29</v>
-      </c>
-      <c r="U26" t="n">
         <v>76</v>
       </c>
     </row>
@@ -3401,51 +3005,42 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.859375</v>
+        <v>165</v>
       </c>
       <c r="G27" t="n">
         <v>0.859375</v>
       </c>
       <c r="H27" t="n">
-        <v>101</v>
+        <v>0.859375</v>
       </c>
       <c r="I27" t="n">
-        <v>94</v>
+        <v>0.8936170212765957</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8316831683168316</v>
+        <v>0.8615384615384615</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8615384615384615</v>
+        <v>0.826530612244898</v>
       </c>
       <c r="M27" t="n">
-        <v>91</v>
+        <v>0.8901098901098901</v>
       </c>
       <c r="N27" t="n">
-        <v>98</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="O27" t="n">
-        <v>0.826530612244898</v>
+        <v>84</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8901098901098901</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8571428571428572</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>84</v>
-      </c>
-      <c r="S27" t="n">
-        <v>17</v>
-      </c>
-      <c r="T27" t="n">
-        <v>10</v>
-      </c>
-      <c r="U27" t="n">
         <v>81</v>
       </c>
     </row>
@@ -3468,51 +3063,42 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8541666666666666</v>
+        <v>164</v>
       </c>
       <c r="G28" t="n">
         <v>0.8541666666666666</v>
       </c>
       <c r="H28" t="n">
-        <v>95</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I28" t="n">
-        <v>95</v>
+        <v>0.8526315789473684</v>
       </c>
       <c r="J28" t="n">
         <v>0.8526315789473684</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.8526315789473685</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8526315789473685</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="M28" t="n">
-        <v>97</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="N28" t="n">
-        <v>97</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8556701030927835</v>
+        <v>81</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8556701030927835</v>
+        <v>14</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8556701030927835</v>
+        <v>14</v>
       </c>
       <c r="R28" t="n">
-        <v>81</v>
-      </c>
-      <c r="S28" t="n">
-        <v>14</v>
-      </c>
-      <c r="T28" t="n">
-        <v>14</v>
-      </c>
-      <c r="U28" t="n">
         <v>83</v>
       </c>
     </row>
@@ -3535,51 +3121,42 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.671875</v>
+        <v>129</v>
       </c>
       <c r="G29" t="n">
         <v>0.671875</v>
       </c>
       <c r="H29" t="n">
-        <v>90</v>
+        <v>0.671875</v>
       </c>
       <c r="I29" t="n">
-        <v>129</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7123287671232877</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7123287671232877</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="M29" t="n">
-        <v>102</v>
+        <v>0.5</v>
       </c>
       <c r="N29" t="n">
-        <v>63</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8095238095238095</v>
+        <v>78</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.6181818181818182</v>
+        <v>51</v>
       </c>
       <c r="R29" t="n">
-        <v>78</v>
-      </c>
-      <c r="S29" t="n">
-        <v>12</v>
-      </c>
-      <c r="T29" t="n">
-        <v>51</v>
-      </c>
-      <c r="U29" t="n">
         <v>51</v>
       </c>
     </row>
@@ -3602,51 +3179,42 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G30" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H30" t="n">
-        <v>99</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I30" t="n">
-        <v>110</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8080808080808081</v>
+        <v>0.7655502392344496</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7655502392344496</v>
+        <v>0.7682926829268293</v>
       </c>
       <c r="M30" t="n">
-        <v>93</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="N30" t="n">
-        <v>82</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7682926829268293</v>
+        <v>80</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6774193548387096</v>
+        <v>19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.7199999999999999</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
-        <v>80</v>
-      </c>
-      <c r="S30" t="n">
-        <v>19</v>
-      </c>
-      <c r="T30" t="n">
-        <v>30</v>
-      </c>
-      <c r="U30" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3669,51 +3237,42 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7083333333333334</v>
+        <v>136</v>
       </c>
       <c r="G31" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="H31" t="n">
-        <v>92</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I31" t="n">
-        <v>128</v>
+        <v>0.640625</v>
       </c>
       <c r="J31" t="n">
-        <v>0.640625</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.7454545454545454</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7454545454545454</v>
+        <v>0.84375</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0.54</v>
       </c>
       <c r="N31" t="n">
-        <v>64</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="O31" t="n">
-        <v>0.84375</v>
+        <v>82</v>
       </c>
       <c r="P31" t="n">
-        <v>0.54</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.6585365853658537</v>
+        <v>46</v>
       </c>
       <c r="R31" t="n">
-        <v>82</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="n">
-        <v>46</v>
-      </c>
-      <c r="U31" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3736,51 +3295,42 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G32" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>89</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I32" t="n">
-        <v>77</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7078651685393258</v>
+        <v>0.7590361445783134</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7590361445783134</v>
+        <v>0.7739130434782608</v>
       </c>
       <c r="M32" t="n">
-        <v>103</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="N32" t="n">
-        <v>115</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7739130434782608</v>
+        <v>63</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8640776699029126</v>
+        <v>26</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8165137614678899</v>
+        <v>14</v>
       </c>
       <c r="R32" t="n">
-        <v>63</v>
-      </c>
-      <c r="S32" t="n">
-        <v>26</v>
-      </c>
-      <c r="T32" t="n">
-        <v>14</v>
-      </c>
-      <c r="U32" t="n">
         <v>89</v>
       </c>
     </row>
@@ -3803,51 +3353,42 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.875</v>
+        <v>168</v>
       </c>
       <c r="G33" t="n">
         <v>0.875</v>
       </c>
       <c r="H33" t="n">
-        <v>94</v>
+        <v>0.875</v>
       </c>
       <c r="I33" t="n">
-        <v>84</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.8651685393258427</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8651685393258427</v>
+        <v>0.8425925925925926</v>
       </c>
       <c r="M33" t="n">
-        <v>98</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="N33" t="n">
-        <v>108</v>
+        <v>0.883495145631068</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8425925925925926</v>
+        <v>77</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9285714285714286</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.883495145631068</v>
+        <v>7</v>
       </c>
       <c r="R33" t="n">
-        <v>77</v>
-      </c>
-      <c r="S33" t="n">
-        <v>17</v>
-      </c>
-      <c r="T33" t="n">
-        <v>7</v>
-      </c>
-      <c r="U33" t="n">
         <v>91</v>
       </c>
     </row>
@@ -3870,51 +3411,42 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G34" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>93</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I34" t="n">
-        <v>89</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7912087912087912</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="M34" t="n">
-        <v>99</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="N34" t="n">
-        <v>103</v>
+        <v>0.8118811881188118</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7961165048543689</v>
+        <v>72</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8282828282828283</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8118811881188118</v>
+        <v>17</v>
       </c>
       <c r="R34" t="n">
-        <v>72</v>
-      </c>
-      <c r="S34" t="n">
-        <v>21</v>
-      </c>
-      <c r="T34" t="n">
-        <v>17</v>
-      </c>
-      <c r="U34" t="n">
         <v>82</v>
       </c>
     </row>
@@ -3937,51 +3469,42 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G35" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H35" t="n">
-        <v>92</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I35" t="n">
-        <v>134</v>
+        <v>0.6567164179104478</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6567164179104478</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.7787610619469028</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7787610619469028</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0.54</v>
       </c>
       <c r="N35" t="n">
-        <v>58</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9310344827586207</v>
+        <v>88</v>
       </c>
       <c r="P35" t="n">
-        <v>0.54</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.6835443037974683</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
-        <v>88</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>46</v>
-      </c>
-      <c r="U35" t="n">
         <v>54</v>
       </c>
     </row>
@@ -4004,51 +3527,42 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G36" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>84</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I36" t="n">
-        <v>110</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7731958762886597</v>
       </c>
       <c r="L36" t="n">
-        <v>0.7731958762886597</v>
+        <v>0.8902439024390244</v>
       </c>
       <c r="M36" t="n">
-        <v>108</v>
+        <v>0.6759259259259259</v>
       </c>
       <c r="N36" t="n">
-        <v>82</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8902439024390244</v>
+        <v>75</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6759259259259259</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.7684210526315789</v>
+        <v>35</v>
       </c>
       <c r="R36" t="n">
-        <v>75</v>
-      </c>
-      <c r="S36" t="n">
-        <v>9</v>
-      </c>
-      <c r="T36" t="n">
-        <v>35</v>
-      </c>
-      <c r="U36" t="n">
         <v>73</v>
       </c>
     </row>
@@ -4071,51 +3585,42 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G37" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>86</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.73</v>
       </c>
       <c r="K37" t="n">
-        <v>0.73</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7849462365591398</v>
+        <v>0.7452830188679245</v>
       </c>
       <c r="M37" t="n">
-        <v>92</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="N37" t="n">
-        <v>106</v>
+        <v>0.7979797979797979</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7452830188679245</v>
+        <v>73</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8586956521739131</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.7979797979797979</v>
+        <v>13</v>
       </c>
       <c r="R37" t="n">
-        <v>73</v>
-      </c>
-      <c r="S37" t="n">
-        <v>27</v>
-      </c>
-      <c r="T37" t="n">
-        <v>13</v>
-      </c>
-      <c r="U37" t="n">
         <v>79</v>
       </c>
     </row>
@@ -4138,51 +3643,42 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7552083333333334</v>
+        <v>145</v>
       </c>
       <c r="G38" t="n">
         <v>0.7552083333333334</v>
       </c>
       <c r="H38" t="n">
-        <v>98</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I38" t="n">
-        <v>81</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="K38" t="n">
-        <v>0.673469387755102</v>
+        <v>0.7374301675977653</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7374301675977653</v>
+        <v>0.7117117117117117</v>
       </c>
       <c r="M38" t="n">
-        <v>94</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="N38" t="n">
-        <v>111</v>
+        <v>0.7707317073170732</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7117117117117117</v>
+        <v>66</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8404255319148937</v>
+        <v>32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.7707317073170732</v>
+        <v>15</v>
       </c>
       <c r="R38" t="n">
-        <v>66</v>
-      </c>
-      <c r="S38" t="n">
-        <v>32</v>
-      </c>
-      <c r="T38" t="n">
-        <v>15</v>
-      </c>
-      <c r="U38" t="n">
         <v>79</v>
       </c>
     </row>
@@ -4205,51 +3701,42 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G39" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H39" t="n">
-        <v>84</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I39" t="n">
-        <v>111</v>
+        <v>0.6396396396396397</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.8452380952380952</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.7282051282051283</v>
       </c>
       <c r="L39" t="n">
-        <v>0.7282051282051283</v>
+        <v>0.8395061728395061</v>
       </c>
       <c r="M39" t="n">
-        <v>108</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="N39" t="n">
-        <v>81</v>
+        <v>0.7195767195767196</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8395061728395061</v>
+        <v>71</v>
       </c>
       <c r="P39" t="n">
-        <v>0.6296296296296297</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7195767195767196</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
-        <v>71</v>
-      </c>
-      <c r="S39" t="n">
-        <v>13</v>
-      </c>
-      <c r="T39" t="n">
-        <v>40</v>
-      </c>
-      <c r="U39" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4272,51 +3759,42 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G40" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I40" t="n">
-        <v>122</v>
+        <v>0.6967213114754098</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6967213114754098</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8673469387755102</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.8142857142857143</v>
       </c>
       <c r="M40" t="n">
-        <v>94</v>
+        <v>0.6063829787234043</v>
       </c>
       <c r="N40" t="n">
-        <v>70</v>
+        <v>0.6951219512195123</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8142857142857143</v>
+        <v>85</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6063829787234043</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6951219512195123</v>
+        <v>37</v>
       </c>
       <c r="R40" t="n">
-        <v>85</v>
-      </c>
-      <c r="S40" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" t="n">
-        <v>37</v>
-      </c>
-      <c r="U40" t="n">
         <v>57</v>
       </c>
     </row>
@@ -4339,51 +3817,42 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8333333333333334</v>
+        <v>160</v>
       </c>
       <c r="G41" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="H41" t="n">
-        <v>105</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I41" t="n">
-        <v>89</v>
+        <v>0.9101123595505618</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9101123595505618</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.8350515463917525</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8350515463917525</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="M41" t="n">
-        <v>87</v>
+        <v>0.9080459770114943</v>
       </c>
       <c r="N41" t="n">
-        <v>103</v>
+        <v>0.8315789473684211</v>
       </c>
       <c r="O41" t="n">
-        <v>0.7669902912621359</v>
+        <v>81</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9080459770114943</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.8315789473684211</v>
+        <v>8</v>
       </c>
       <c r="R41" t="n">
-        <v>81</v>
-      </c>
-      <c r="S41" t="n">
-        <v>24</v>
-      </c>
-      <c r="T41" t="n">
-        <v>8</v>
-      </c>
-      <c r="U41" t="n">
         <v>79</v>
       </c>
     </row>
@@ -4406,51 +3875,42 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6979166666666666</v>
+        <v>134</v>
       </c>
       <c r="G42" t="n">
         <v>0.6979166666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>89</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="I42" t="n">
-        <v>99</v>
+        <v>0.6565656565656566</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6565656565656566</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7303370786516854</v>
+        <v>0.6914893617021276</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6914893617021276</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="M42" t="n">
-        <v>103</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="N42" t="n">
-        <v>93</v>
+        <v>0.7040816326530613</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7419354838709677</v>
+        <v>65</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6699029126213593</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.7040816326530613</v>
+        <v>34</v>
       </c>
       <c r="R42" t="n">
-        <v>65</v>
-      </c>
-      <c r="S42" t="n">
-        <v>24</v>
-      </c>
-      <c r="T42" t="n">
-        <v>34</v>
-      </c>
-      <c r="U42" t="n">
         <v>69</v>
       </c>
     </row>
@@ -4473,51 +3933,42 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G43" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>98</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I43" t="n">
-        <v>88</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7954545454545454</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7526881720430106</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7526881720430106</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M43" t="n">
-        <v>94</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="N43" t="n">
-        <v>104</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7307692307692307</v>
+        <v>70</v>
       </c>
       <c r="P43" t="n">
-        <v>0.8085106382978723</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7676767676767676</v>
+        <v>18</v>
       </c>
       <c r="R43" t="n">
-        <v>70</v>
-      </c>
-      <c r="S43" t="n">
-        <v>28</v>
-      </c>
-      <c r="T43" t="n">
-        <v>18</v>
-      </c>
-      <c r="U43" t="n">
         <v>76</v>
       </c>
     </row>
@@ -4540,51 +3991,42 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G44" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>111</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I44" t="n">
-        <v>114</v>
+        <v>0.7982456140350878</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7982456140350878</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8198198198198198</v>
+        <v>0.8088888888888889</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8088888888888889</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="M44" t="n">
-        <v>81</v>
+        <v>0.7160493827160493</v>
       </c>
       <c r="N44" t="n">
-        <v>78</v>
+        <v>0.7295597484276728</v>
       </c>
       <c r="O44" t="n">
-        <v>0.7435897435897436</v>
+        <v>91</v>
       </c>
       <c r="P44" t="n">
-        <v>0.7160493827160493</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.7295597484276728</v>
+        <v>23</v>
       </c>
       <c r="R44" t="n">
-        <v>91</v>
-      </c>
-      <c r="S44" t="n">
-        <v>20</v>
-      </c>
-      <c r="T44" t="n">
-        <v>23</v>
-      </c>
-      <c r="U44" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4607,51 +4049,42 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8125</v>
+        <v>156</v>
       </c>
       <c r="G45" t="n">
         <v>0.8125</v>
       </c>
       <c r="H45" t="n">
-        <v>95</v>
+        <v>0.8125</v>
       </c>
       <c r="I45" t="n">
-        <v>119</v>
+        <v>0.7478991596638656</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7478991596638656</v>
+        <v>0.9368421052631579</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9368421052631579</v>
+        <v>0.8317757009345795</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8317757009345795</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="M45" t="n">
-        <v>97</v>
+        <v>0.6907216494845361</v>
       </c>
       <c r="N45" t="n">
-        <v>73</v>
+        <v>0.7882352941176471</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9178082191780822</v>
+        <v>89</v>
       </c>
       <c r="P45" t="n">
-        <v>0.6907216494845361</v>
+        <v>6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.7882352941176471</v>
+        <v>30</v>
       </c>
       <c r="R45" t="n">
-        <v>89</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6</v>
-      </c>
-      <c r="T45" t="n">
-        <v>30</v>
-      </c>
-      <c r="U45" t="n">
         <v>67</v>
       </c>
     </row>
@@ -4674,51 +4107,42 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G46" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H46" t="n">
-        <v>102</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I46" t="n">
-        <v>116</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="L46" t="n">
-        <v>0.7889908256880734</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="M46" t="n">
-        <v>90</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N46" t="n">
-        <v>76</v>
+        <v>0.7228915662650601</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7894736842105263</v>
+        <v>86</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6666666666666666</v>
+        <v>16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.7228915662650601</v>
+        <v>30</v>
       </c>
       <c r="R46" t="n">
-        <v>86</v>
-      </c>
-      <c r="S46" t="n">
-        <v>16</v>
-      </c>
-      <c r="T46" t="n">
-        <v>30</v>
-      </c>
-      <c r="U46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4741,51 +4165,42 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8385416666666666</v>
+        <v>161</v>
       </c>
       <c r="G47" t="n">
         <v>0.8385416666666666</v>
       </c>
       <c r="H47" t="n">
-        <v>99</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I47" t="n">
-        <v>86</v>
+        <v>0.8953488372093024</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8953488372093024</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8324324324324325</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8324324324324325</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="M47" t="n">
-        <v>93</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="N47" t="n">
-        <v>106</v>
+        <v>0.8442211055276382</v>
       </c>
       <c r="O47" t="n">
-        <v>0.7924528301886793</v>
+        <v>77</v>
       </c>
       <c r="P47" t="n">
-        <v>0.9032258064516129</v>
+        <v>22</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.8442211055276382</v>
+        <v>9</v>
       </c>
       <c r="R47" t="n">
-        <v>77</v>
-      </c>
-      <c r="S47" t="n">
-        <v>22</v>
-      </c>
-      <c r="T47" t="n">
-        <v>9</v>
-      </c>
-      <c r="U47" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4808,51 +4223,42 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G48" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>93</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I48" t="n">
-        <v>118</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6610169491525424</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7393364928909952</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7393364928909952</v>
+        <v>0.7972972972972973</v>
       </c>
       <c r="M48" t="n">
-        <v>99</v>
+        <v>0.5959595959595959</v>
       </c>
       <c r="N48" t="n">
-        <v>74</v>
+        <v>0.6820809248554912</v>
       </c>
       <c r="O48" t="n">
-        <v>0.7972972972972973</v>
+        <v>78</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5959595959595959</v>
+        <v>15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.6820809248554912</v>
+        <v>40</v>
       </c>
       <c r="R48" t="n">
-        <v>78</v>
-      </c>
-      <c r="S48" t="n">
-        <v>15</v>
-      </c>
-      <c r="T48" t="n">
-        <v>40</v>
-      </c>
-      <c r="U48" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4875,51 +4281,42 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7864583333333334</v>
+        <v>151</v>
       </c>
       <c r="G49" t="n">
         <v>0.7864583333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>87</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I49" t="n">
-        <v>84</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.7471264367816092</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7471264367816092</v>
+        <v>0.760233918128655</v>
       </c>
       <c r="L49" t="n">
-        <v>0.760233918128655</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="M49" t="n">
-        <v>105</v>
+        <v>0.819047619047619</v>
       </c>
       <c r="N49" t="n">
-        <v>108</v>
+        <v>0.8075117370892019</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7962962962962963</v>
+        <v>65</v>
       </c>
       <c r="P49" t="n">
-        <v>0.819047619047619</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.8075117370892019</v>
+        <v>19</v>
       </c>
       <c r="R49" t="n">
-        <v>65</v>
-      </c>
-      <c r="S49" t="n">
-        <v>22</v>
-      </c>
-      <c r="T49" t="n">
-        <v>19</v>
-      </c>
-      <c r="U49" t="n">
         <v>86</v>
       </c>
     </row>
@@ -4942,16 +4339,16 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.90625</v>
+        <v>174</v>
       </c>
       <c r="G50" t="n">
         <v>0.90625</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>0.90625</v>
       </c>
       <c r="I50" t="n">
-        <v>88</v>
+        <v>0.8977272727272727</v>
       </c>
       <c r="J50" t="n">
         <v>0.8977272727272727</v>
@@ -4960,33 +4357,24 @@
         <v>0.8977272727272727</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.9134615384615384</v>
       </c>
       <c r="M50" t="n">
-        <v>104</v>
+        <v>0.9134615384615384</v>
       </c>
       <c r="N50" t="n">
-        <v>104</v>
+        <v>0.9134615384615384</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9134615384615384</v>
+        <v>79</v>
       </c>
       <c r="P50" t="n">
-        <v>0.9134615384615384</v>
+        <v>9</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9134615384615384</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
-        <v>79</v>
-      </c>
-      <c r="S50" t="n">
-        <v>9</v>
-      </c>
-      <c r="T50" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" t="n">
         <v>95</v>
       </c>
     </row>
@@ -5009,51 +4397,42 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8645833333333334</v>
+        <v>166</v>
       </c>
       <c r="G51" t="n">
         <v>0.8645833333333334</v>
       </c>
       <c r="H51" t="n">
-        <v>88</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="I51" t="n">
-        <v>98</v>
+        <v>0.8163265306122449</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8163265306122449</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8602150537634408</v>
       </c>
       <c r="L51" t="n">
-        <v>0.8602150537634408</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="M51" t="n">
-        <v>104</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="N51" t="n">
-        <v>94</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9148936170212766</v>
+        <v>80</v>
       </c>
       <c r="P51" t="n">
-        <v>0.8269230769230769</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8686868686868686</v>
+        <v>18</v>
       </c>
       <c r="R51" t="n">
-        <v>80</v>
-      </c>
-      <c r="S51" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>18</v>
-      </c>
-      <c r="U51" t="n">
         <v>86</v>
       </c>
     </row>
@@ -5076,51 +4455,42 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G52" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H52" t="n">
-        <v>93</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I52" t="n">
-        <v>111</v>
+        <v>0.7657657657657657</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7657657657657657</v>
+        <v>0.9139784946236559</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9139784946236559</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="M52" t="n">
-        <v>99</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="N52" t="n">
-        <v>81</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9012345679012346</v>
+        <v>85</v>
       </c>
       <c r="P52" t="n">
-        <v>0.7373737373737373</v>
+        <v>8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.8111111111111111</v>
+        <v>26</v>
       </c>
       <c r="R52" t="n">
-        <v>85</v>
-      </c>
-      <c r="S52" t="n">
-        <v>8</v>
-      </c>
-      <c r="T52" t="n">
-        <v>26</v>
-      </c>
-      <c r="U52" t="n">
         <v>73</v>
       </c>
     </row>
@@ -5143,51 +4513,42 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G53" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H53" t="n">
-        <v>95</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I53" t="n">
-        <v>128</v>
+        <v>0.6796875</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6796875</v>
+        <v>0.9157894736842105</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9157894736842105</v>
+        <v>0.7802690582959642</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7802690582959642</v>
+        <v>0.875</v>
       </c>
       <c r="M53" t="n">
-        <v>97</v>
+        <v>0.5773195876288659</v>
       </c>
       <c r="N53" t="n">
-        <v>64</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="O53" t="n">
-        <v>0.875</v>
+        <v>87</v>
       </c>
       <c r="P53" t="n">
-        <v>0.5773195876288659</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6956521739130435</v>
+        <v>41</v>
       </c>
       <c r="R53" t="n">
-        <v>87</v>
-      </c>
-      <c r="S53" t="n">
-        <v>8</v>
-      </c>
-      <c r="T53" t="n">
-        <v>41</v>
-      </c>
-      <c r="U53" t="n">
         <v>56</v>
       </c>
     </row>
@@ -5210,51 +4571,42 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G54" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H54" t="n">
-        <v>99</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I54" t="n">
-        <v>127</v>
+        <v>0.7559055118110236</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7559055118110236</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.8495575221238938</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8495575221238938</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="M54" t="n">
-        <v>93</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N54" t="n">
-        <v>65</v>
+        <v>0.7848101265822784</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9538461538461539</v>
+        <v>96</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6666666666666666</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.7848101265822784</v>
+        <v>31</v>
       </c>
       <c r="R54" t="n">
-        <v>96</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3</v>
-      </c>
-      <c r="T54" t="n">
-        <v>31</v>
-      </c>
-      <c r="U54" t="n">
         <v>62</v>
       </c>
     </row>
@@ -5277,51 +4629,42 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G55" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I55" t="n">
-        <v>97</v>
+        <v>0.7731958762886598</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8021390374331551</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8021390374331551</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M55" t="n">
-        <v>102</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="N55" t="n">
-        <v>95</v>
+        <v>0.8121827411167514</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8421052631578947</v>
+        <v>75</v>
       </c>
       <c r="P55" t="n">
-        <v>0.7843137254901961</v>
+        <v>15</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8121827411167514</v>
+        <v>22</v>
       </c>
       <c r="R55" t="n">
-        <v>75</v>
-      </c>
-      <c r="S55" t="n">
-        <v>15</v>
-      </c>
-      <c r="T55" t="n">
-        <v>22</v>
-      </c>
-      <c r="U55" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5344,51 +4687,42 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G56" t="n">
         <v>0.828125</v>
       </c>
       <c r="H56" t="n">
-        <v>94</v>
+        <v>0.828125</v>
       </c>
       <c r="I56" t="n">
-        <v>111</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="J56" t="n">
-        <v>0.7747747747747747</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.8390243902439024</v>
       </c>
       <c r="L56" t="n">
-        <v>0.8390243902439024</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="M56" t="n">
-        <v>98</v>
+        <v>0.7448979591836735</v>
       </c>
       <c r="N56" t="n">
-        <v>81</v>
+        <v>0.8156424581005587</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9012345679012346</v>
+        <v>86</v>
       </c>
       <c r="P56" t="n">
-        <v>0.7448979591836735</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8156424581005587</v>
+        <v>25</v>
       </c>
       <c r="R56" t="n">
-        <v>86</v>
-      </c>
-      <c r="S56" t="n">
-        <v>8</v>
-      </c>
-      <c r="T56" t="n">
-        <v>25</v>
-      </c>
-      <c r="U56" t="n">
         <v>73</v>
       </c>
     </row>
@@ -5411,51 +4745,42 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G57" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H57" t="n">
-        <v>95</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I57" t="n">
-        <v>106</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.8631578947368421</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.8159203980099502</v>
       </c>
       <c r="L57" t="n">
-        <v>0.8159203980099502</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="M57" t="n">
-        <v>97</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="N57" t="n">
-        <v>86</v>
+        <v>0.7978142076502732</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8488372093023255</v>
+        <v>82</v>
       </c>
       <c r="P57" t="n">
-        <v>0.7525773195876289</v>
+        <v>13</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.7978142076502732</v>
+        <v>24</v>
       </c>
       <c r="R57" t="n">
-        <v>82</v>
-      </c>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>24</v>
-      </c>
-      <c r="U57" t="n">
         <v>73</v>
       </c>
     </row>
@@ -5478,51 +4803,42 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8385416666666666</v>
+        <v>161</v>
       </c>
       <c r="G58" t="n">
         <v>0.8385416666666666</v>
       </c>
       <c r="H58" t="n">
-        <v>91</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I58" t="n">
-        <v>106</v>
+        <v>0.7830188679245284</v>
       </c>
       <c r="J58" t="n">
-        <v>0.7830188679245284</v>
+        <v>0.9120879120879121</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9120879120879121</v>
+        <v>0.8426395939086294</v>
       </c>
       <c r="L58" t="n">
-        <v>0.8426395939086294</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="M58" t="n">
-        <v>101</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="N58" t="n">
-        <v>86</v>
+        <v>0.8342245989304812</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9069767441860465</v>
+        <v>83</v>
       </c>
       <c r="P58" t="n">
-        <v>0.7722772277227723</v>
+        <v>8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.8342245989304812</v>
+        <v>23</v>
       </c>
       <c r="R58" t="n">
-        <v>83</v>
-      </c>
-      <c r="S58" t="n">
-        <v>8</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23</v>
-      </c>
-      <c r="U58" t="n">
         <v>78</v>
       </c>
     </row>
@@ -5545,51 +4861,42 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G59" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H59" t="n">
-        <v>88</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I59" t="n">
-        <v>99</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="J59" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8522727272727273</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8522727272727273</v>
+        <v>0.8021390374331552</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8021390374331552</v>
+        <v>0.8602150537634409</v>
       </c>
       <c r="M59" t="n">
-        <v>104</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="N59" t="n">
-        <v>93</v>
+        <v>0.8121827411167513</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8602150537634409</v>
+        <v>75</v>
       </c>
       <c r="P59" t="n">
-        <v>0.7692307692307693</v>
+        <v>13</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.8121827411167513</v>
+        <v>24</v>
       </c>
       <c r="R59" t="n">
-        <v>75</v>
-      </c>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>24</v>
-      </c>
-      <c r="U59" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5612,51 +4919,42 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7864583333333334</v>
+        <v>151</v>
       </c>
       <c r="G60" t="n">
         <v>0.7864583333333334</v>
       </c>
       <c r="H60" t="n">
-        <v>111</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I60" t="n">
-        <v>112</v>
+        <v>0.8125</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8125</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8198198198198198</v>
+        <v>0.8161434977578474</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8161434977578474</v>
+        <v>0.75</v>
       </c>
       <c r="M60" t="n">
-        <v>81</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="N60" t="n">
-        <v>80</v>
+        <v>0.7453416149068324</v>
       </c>
       <c r="O60" t="n">
-        <v>0.75</v>
+        <v>91</v>
       </c>
       <c r="P60" t="n">
-        <v>0.7407407407407407</v>
+        <v>20</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.7453416149068324</v>
+        <v>21</v>
       </c>
       <c r="R60" t="n">
-        <v>91</v>
-      </c>
-      <c r="S60" t="n">
-        <v>20</v>
-      </c>
-      <c r="T60" t="n">
-        <v>21</v>
-      </c>
-      <c r="U60" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5679,53 +4977,44 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G61" t="n">
         <v>0.78125</v>
       </c>
       <c r="H61" t="n">
-        <v>98</v>
+        <v>0.78125</v>
       </c>
       <c r="I61" t="n">
-        <v>94</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="J61" t="n">
+        <v>0.7653061224489796</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.7812500000000001</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.7653061224489796</v>
+      </c>
+      <c r="M61" t="n">
         <v>0.7978723404255319</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.7653061224489796</v>
-      </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>0.7812500000000001</v>
       </c>
-      <c r="M61" t="n">
-        <v>94</v>
-      </c>
-      <c r="N61" t="n">
-        <v>98</v>
-      </c>
       <c r="O61" t="n">
-        <v>0.7653061224489796</v>
+        <v>75</v>
       </c>
       <c r="P61" t="n">
-        <v>0.7978723404255319</v>
+        <v>23</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.7812500000000001</v>
+        <v>19</v>
       </c>
       <c r="R61" t="n">
         <v>75</v>
       </c>
-      <c r="S61" t="n">
-        <v>23</v>
-      </c>
-      <c r="T61" t="n">
-        <v>19</v>
-      </c>
-      <c r="U61" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5746,51 +5035,42 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G62" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>106</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I62" t="n">
-        <v>124</v>
+        <v>0.75</v>
       </c>
       <c r="J62" t="n">
-        <v>0.75</v>
+        <v>0.8773584905660378</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8773584905660378</v>
+        <v>0.8086956521739131</v>
       </c>
       <c r="L62" t="n">
-        <v>0.8086956521739131</v>
+        <v>0.8088235294117647</v>
       </c>
       <c r="M62" t="n">
-        <v>86</v>
+        <v>0.6395348837209303</v>
       </c>
       <c r="N62" t="n">
-        <v>68</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8088235294117647</v>
+        <v>93</v>
       </c>
       <c r="P62" t="n">
-        <v>0.6395348837209303</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.7142857142857143</v>
+        <v>31</v>
       </c>
       <c r="R62" t="n">
-        <v>93</v>
-      </c>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>31</v>
-      </c>
-      <c r="U62" t="n">
         <v>55</v>
       </c>
     </row>
@@ -5813,51 +5093,42 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G63" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H63" t="n">
-        <v>88</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I63" t="n">
-        <v>108</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7959183673469388</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="M63" t="n">
-        <v>104</v>
+        <v>0.7115384615384616</v>
       </c>
       <c r="N63" t="n">
-        <v>84</v>
+        <v>0.7872340425531914</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8809523809523809</v>
+        <v>78</v>
       </c>
       <c r="P63" t="n">
-        <v>0.7115384615384616</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.7872340425531914</v>
+        <v>30</v>
       </c>
       <c r="R63" t="n">
-        <v>78</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="n">
-        <v>30</v>
-      </c>
-      <c r="U63" t="n">
         <v>74</v>
       </c>
     </row>
@@ -5880,51 +5151,42 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.640625</v>
+        <v>123</v>
       </c>
       <c r="G64" t="n">
         <v>0.640625</v>
       </c>
       <c r="H64" t="n">
-        <v>91</v>
+        <v>0.640625</v>
       </c>
       <c r="I64" t="n">
-        <v>122</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7912087912087912</v>
+        <v>0.6760563380281689</v>
       </c>
       <c r="L64" t="n">
-        <v>0.6760563380281689</v>
+        <v>0.7285714285714285</v>
       </c>
       <c r="M64" t="n">
-        <v>101</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="N64" t="n">
-        <v>70</v>
+        <v>0.5964912280701754</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7285714285714285</v>
+        <v>72</v>
       </c>
       <c r="P64" t="n">
-        <v>0.504950495049505</v>
+        <v>19</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.5964912280701754</v>
+        <v>50</v>
       </c>
       <c r="R64" t="n">
-        <v>72</v>
-      </c>
-      <c r="S64" t="n">
-        <v>19</v>
-      </c>
-      <c r="T64" t="n">
-        <v>50</v>
-      </c>
-      <c r="U64" t="n">
         <v>51</v>
       </c>
     </row>
@@ -5947,51 +5209,42 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G65" t="n">
         <v>0.828125</v>
       </c>
       <c r="H65" t="n">
-        <v>95</v>
+        <v>0.828125</v>
       </c>
       <c r="I65" t="n">
-        <v>102</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="J65" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8631578947368421</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.83248730964467</v>
       </c>
       <c r="L65" t="n">
-        <v>0.83248730964467</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="M65" t="n">
-        <v>97</v>
+        <v>0.7938144329896907</v>
       </c>
       <c r="N65" t="n">
-        <v>90</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="O65" t="n">
-        <v>0.8555555555555555</v>
+        <v>82</v>
       </c>
       <c r="P65" t="n">
-        <v>0.7938144329896907</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.8235294117647058</v>
+        <v>20</v>
       </c>
       <c r="R65" t="n">
-        <v>82</v>
-      </c>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>20</v>
-      </c>
-      <c r="U65" t="n">
         <v>77</v>
       </c>
     </row>
@@ -6014,51 +5267,42 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8125</v>
+        <v>156</v>
       </c>
       <c r="G66" t="n">
         <v>0.8125</v>
       </c>
       <c r="H66" t="n">
-        <v>83</v>
+        <v>0.8125</v>
       </c>
       <c r="I66" t="n">
-        <v>91</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7582417582417582</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="L66" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="M66" t="n">
-        <v>109</v>
+        <v>0.7981651376146789</v>
       </c>
       <c r="N66" t="n">
-        <v>101</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8613861386138614</v>
+        <v>69</v>
       </c>
       <c r="P66" t="n">
-        <v>0.7981651376146789</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.8285714285714286</v>
+        <v>22</v>
       </c>
       <c r="R66" t="n">
-        <v>69</v>
-      </c>
-      <c r="S66" t="n">
-        <v>14</v>
-      </c>
-      <c r="T66" t="n">
-        <v>22</v>
-      </c>
-      <c r="U66" t="n">
         <v>87</v>
       </c>
     </row>
@@ -6081,51 +5325,42 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7552083333333334</v>
+        <v>145</v>
       </c>
       <c r="G67" t="n">
         <v>0.7552083333333334</v>
       </c>
       <c r="H67" t="n">
-        <v>92</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I67" t="n">
-        <v>101</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="K67" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.7564766839378239</v>
       </c>
       <c r="L67" t="n">
-        <v>0.7564766839378239</v>
+        <v>0.7912087912087912</v>
       </c>
       <c r="M67" t="n">
-        <v>100</v>
+        <v>0.72</v>
       </c>
       <c r="N67" t="n">
-        <v>91</v>
+        <v>0.7539267015706805</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7912087912087912</v>
+        <v>73</v>
       </c>
       <c r="P67" t="n">
-        <v>0.72</v>
+        <v>19</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.7539267015706805</v>
+        <v>28</v>
       </c>
       <c r="R67" t="n">
-        <v>73</v>
-      </c>
-      <c r="S67" t="n">
-        <v>19</v>
-      </c>
-      <c r="T67" t="n">
-        <v>28</v>
-      </c>
-      <c r="U67" t="n">
         <v>72</v>
       </c>
     </row>
@@ -6148,51 +5383,42 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G68" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H68" t="n">
-        <v>98</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I68" t="n">
-        <v>104</v>
+        <v>0.7596153846153846</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7596153846153846</v>
+        <v>0.8061224489795918</v>
       </c>
       <c r="K68" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.7821782178217821</v>
       </c>
       <c r="L68" t="n">
-        <v>0.7821782178217821</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="M68" t="n">
-        <v>94</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="N68" t="n">
-        <v>88</v>
+        <v>0.7582417582417583</v>
       </c>
       <c r="O68" t="n">
-        <v>0.7840909090909091</v>
+        <v>79</v>
       </c>
       <c r="P68" t="n">
-        <v>0.7340425531914894</v>
+        <v>19</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7582417582417583</v>
+        <v>25</v>
       </c>
       <c r="R68" t="n">
-        <v>79</v>
-      </c>
-      <c r="S68" t="n">
-        <v>19</v>
-      </c>
-      <c r="T68" t="n">
-        <v>25</v>
-      </c>
-      <c r="U68" t="n">
         <v>69</v>
       </c>
     </row>
@@ -6215,51 +5441,42 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G69" t="n">
         <v>0.796875</v>
       </c>
       <c r="H69" t="n">
-        <v>94</v>
+        <v>0.796875</v>
       </c>
       <c r="I69" t="n">
-        <v>87</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.7553191489361702</v>
       </c>
       <c r="K69" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.7845303867403314</v>
       </c>
       <c r="L69" t="n">
-        <v>0.7845303867403314</v>
+        <v>0.780952380952381</v>
       </c>
       <c r="M69" t="n">
-        <v>98</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="N69" t="n">
-        <v>105</v>
+        <v>0.8078817733990147</v>
       </c>
       <c r="O69" t="n">
-        <v>0.780952380952381</v>
+        <v>71</v>
       </c>
       <c r="P69" t="n">
-        <v>0.8367346938775511</v>
+        <v>23</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.8078817733990147</v>
+        <v>16</v>
       </c>
       <c r="R69" t="n">
-        <v>71</v>
-      </c>
-      <c r="S69" t="n">
-        <v>23</v>
-      </c>
-      <c r="T69" t="n">
-        <v>16</v>
-      </c>
-      <c r="U69" t="n">
         <v>82</v>
       </c>
     </row>
@@ -6282,51 +5499,42 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G70" t="n">
         <v>0.796875</v>
       </c>
       <c r="H70" t="n">
-        <v>83</v>
+        <v>0.796875</v>
       </c>
       <c r="I70" t="n">
-        <v>94</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="L70" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M70" t="n">
-        <v>109</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="N70" t="n">
-        <v>98</v>
+        <v>0.8115942028985508</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8571428571428571</v>
+        <v>69</v>
       </c>
       <c r="P70" t="n">
-        <v>0.7706422018348624</v>
+        <v>14</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.8115942028985508</v>
+        <v>25</v>
       </c>
       <c r="R70" t="n">
-        <v>69</v>
-      </c>
-      <c r="S70" t="n">
-        <v>14</v>
-      </c>
-      <c r="T70" t="n">
-        <v>25</v>
-      </c>
-      <c r="U70" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6349,51 +5557,42 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G71" t="n">
         <v>0.828125</v>
       </c>
       <c r="H71" t="n">
-        <v>93</v>
+        <v>0.828125</v>
       </c>
       <c r="I71" t="n">
-        <v>86</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7849462365591398</v>
+        <v>0.8156424581005587</v>
       </c>
       <c r="L71" t="n">
-        <v>0.8156424581005587</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="M71" t="n">
-        <v>99</v>
+        <v>0.8686868686868687</v>
       </c>
       <c r="N71" t="n">
-        <v>106</v>
+        <v>0.8390243902439025</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8113207547169812</v>
+        <v>73</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8686868686868687</v>
+        <v>20</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.8390243902439025</v>
+        <v>13</v>
       </c>
       <c r="R71" t="n">
-        <v>73</v>
-      </c>
-      <c r="S71" t="n">
-        <v>20</v>
-      </c>
-      <c r="T71" t="n">
-        <v>13</v>
-      </c>
-      <c r="U71" t="n">
         <v>86</v>
       </c>
     </row>
@@ -6416,51 +5615,42 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G72" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H72" t="n">
-        <v>101</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I72" t="n">
-        <v>118</v>
+        <v>0.7033898305084746</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7033898305084746</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="K72" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.7579908675799087</v>
       </c>
       <c r="L72" t="n">
-        <v>0.7579908675799087</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="M72" t="n">
-        <v>91</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N72" t="n">
-        <v>74</v>
+        <v>0.6787878787878788</v>
       </c>
       <c r="O72" t="n">
-        <v>0.7567567567567568</v>
+        <v>83</v>
       </c>
       <c r="P72" t="n">
-        <v>0.6153846153846154</v>
+        <v>18</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.6787878787878788</v>
+        <v>35</v>
       </c>
       <c r="R72" t="n">
-        <v>83</v>
-      </c>
-      <c r="S72" t="n">
-        <v>18</v>
-      </c>
-      <c r="T72" t="n">
-        <v>35</v>
-      </c>
-      <c r="U72" t="n">
         <v>56</v>
       </c>
     </row>
@@ -6483,51 +5673,42 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8697916666666666</v>
+        <v>167</v>
       </c>
       <c r="G73" t="n">
         <v>0.8697916666666666</v>
       </c>
       <c r="H73" t="n">
-        <v>105</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="I73" t="n">
-        <v>118</v>
+        <v>0.8389830508474576</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8389830508474576</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.8878923766816144</v>
       </c>
       <c r="L73" t="n">
-        <v>0.8878923766816144</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="M73" t="n">
-        <v>87</v>
+        <v>0.7816091954022989</v>
       </c>
       <c r="N73" t="n">
-        <v>74</v>
+        <v>0.84472049689441</v>
       </c>
       <c r="O73" t="n">
-        <v>0.918918918918919</v>
+        <v>99</v>
       </c>
       <c r="P73" t="n">
-        <v>0.7816091954022989</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.84472049689441</v>
+        <v>19</v>
       </c>
       <c r="R73" t="n">
-        <v>99</v>
-      </c>
-      <c r="S73" t="n">
-        <v>6</v>
-      </c>
-      <c r="T73" t="n">
-        <v>19</v>
-      </c>
-      <c r="U73" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6550,51 +5731,42 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.71875</v>
+        <v>138</v>
       </c>
       <c r="G74" t="n">
         <v>0.71875</v>
       </c>
       <c r="H74" t="n">
-        <v>84</v>
+        <v>0.71875</v>
       </c>
       <c r="I74" t="n">
-        <v>114</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="J74" t="n">
-        <v>0.631578947368421</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K74" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L74" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M74" t="n">
-        <v>108</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="N74" t="n">
-        <v>78</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8461538461538461</v>
+        <v>72</v>
       </c>
       <c r="P74" t="n">
-        <v>0.6111111111111112</v>
+        <v>12</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.7096774193548387</v>
+        <v>42</v>
       </c>
       <c r="R74" t="n">
-        <v>72</v>
-      </c>
-      <c r="S74" t="n">
-        <v>12</v>
-      </c>
-      <c r="T74" t="n">
-        <v>42</v>
-      </c>
-      <c r="U74" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6617,51 +5789,42 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G75" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H75" t="n">
-        <v>99</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I75" t="n">
-        <v>76</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="J75" t="n">
-        <v>0.868421052631579</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7542857142857142</v>
       </c>
       <c r="L75" t="n">
-        <v>0.7542857142857142</v>
+        <v>0.7155172413793104</v>
       </c>
       <c r="M75" t="n">
-        <v>93</v>
+        <v>0.8924731182795699</v>
       </c>
       <c r="N75" t="n">
-        <v>116</v>
+        <v>0.7942583732057416</v>
       </c>
       <c r="O75" t="n">
-        <v>0.7155172413793104</v>
+        <v>66</v>
       </c>
       <c r="P75" t="n">
-        <v>0.8924731182795699</v>
+        <v>33</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7942583732057416</v>
+        <v>10</v>
       </c>
       <c r="R75" t="n">
-        <v>66</v>
-      </c>
-      <c r="S75" t="n">
-        <v>33</v>
-      </c>
-      <c r="T75" t="n">
-        <v>10</v>
-      </c>
-      <c r="U75" t="n">
         <v>83</v>
       </c>
     </row>
@@ -6684,51 +5847,42 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8645833333333334</v>
+        <v>166</v>
       </c>
       <c r="G76" t="n">
         <v>0.8645833333333334</v>
       </c>
       <c r="H76" t="n">
-        <v>99</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="I76" t="n">
-        <v>91</v>
+        <v>0.9010989010989011</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9010989010989011</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="K76" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.8631578947368421</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="M76" t="n">
-        <v>93</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="N76" t="n">
-        <v>101</v>
+        <v>0.8659793814432989</v>
       </c>
       <c r="O76" t="n">
-        <v>0.8316831683168316</v>
+        <v>82</v>
       </c>
       <c r="P76" t="n">
-        <v>0.9032258064516129</v>
+        <v>17</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.8659793814432989</v>
+        <v>9</v>
       </c>
       <c r="R76" t="n">
-        <v>82</v>
-      </c>
-      <c r="S76" t="n">
-        <v>17</v>
-      </c>
-      <c r="T76" t="n">
-        <v>9</v>
-      </c>
-      <c r="U76" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6751,51 +5905,42 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G77" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>97</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>0.71</v>
       </c>
       <c r="J77" t="n">
-        <v>0.71</v>
+        <v>0.7319587628865979</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7319587628865979</v>
+        <v>0.7208121827411167</v>
       </c>
       <c r="L77" t="n">
-        <v>0.7208121827411167</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="M77" t="n">
-        <v>95</v>
+        <v>0.6947368421052632</v>
       </c>
       <c r="N77" t="n">
-        <v>92</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7173913043478261</v>
+        <v>71</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6947368421052632</v>
+        <v>26</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.7058823529411765</v>
+        <v>29</v>
       </c>
       <c r="R77" t="n">
-        <v>71</v>
-      </c>
-      <c r="S77" t="n">
-        <v>26</v>
-      </c>
-      <c r="T77" t="n">
-        <v>29</v>
-      </c>
-      <c r="U77" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6818,51 +5963,42 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8333333333333334</v>
+        <v>160</v>
       </c>
       <c r="G78" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="H78" t="n">
-        <v>111</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I78" t="n">
-        <v>127</v>
+        <v>0.8110236220472441</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8110236220472441</v>
+        <v>0.9279279279279279</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9279279279279279</v>
+        <v>0.865546218487395</v>
       </c>
       <c r="L78" t="n">
-        <v>0.865546218487395</v>
+        <v>0.8769230769230769</v>
       </c>
       <c r="M78" t="n">
-        <v>81</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="N78" t="n">
-        <v>65</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="O78" t="n">
-        <v>0.8769230769230769</v>
+        <v>103</v>
       </c>
       <c r="P78" t="n">
-        <v>0.7037037037037037</v>
+        <v>8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.7808219178082192</v>
+        <v>24</v>
       </c>
       <c r="R78" t="n">
-        <v>103</v>
-      </c>
-      <c r="S78" t="n">
-        <v>8</v>
-      </c>
-      <c r="T78" t="n">
-        <v>24</v>
-      </c>
-      <c r="U78" t="n">
         <v>57</v>
       </c>
     </row>
@@ -6885,51 +6021,42 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G79" t="n">
         <v>0.796875</v>
       </c>
       <c r="H79" t="n">
-        <v>94</v>
+        <v>0.796875</v>
       </c>
       <c r="I79" t="n">
-        <v>121</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J79" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.8186046511627907</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8186046511627907</v>
+        <v>0.9154929577464789</v>
       </c>
       <c r="M79" t="n">
-        <v>98</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="N79" t="n">
-        <v>71</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9154929577464789</v>
+        <v>88</v>
       </c>
       <c r="P79" t="n">
-        <v>0.6632653061224489</v>
+        <v>6</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.7692307692307692</v>
+        <v>33</v>
       </c>
       <c r="R79" t="n">
-        <v>88</v>
-      </c>
-      <c r="S79" t="n">
-        <v>6</v>
-      </c>
-      <c r="T79" t="n">
-        <v>33</v>
-      </c>
-      <c r="U79" t="n">
         <v>65</v>
       </c>
     </row>
@@ -6952,51 +6079,42 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G80" t="n">
         <v>0.765625</v>
       </c>
       <c r="H80" t="n">
-        <v>87</v>
+        <v>0.765625</v>
       </c>
       <c r="I80" t="n">
-        <v>72</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="J80" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="K80" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="L80" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.75</v>
       </c>
       <c r="M80" t="n">
-        <v>105</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N80" t="n">
-        <v>120</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>0.75</v>
+        <v>57</v>
       </c>
       <c r="P80" t="n">
-        <v>0.8571428571428571</v>
+        <v>30</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.7999999999999999</v>
+        <v>15</v>
       </c>
       <c r="R80" t="n">
-        <v>57</v>
-      </c>
-      <c r="S80" t="n">
-        <v>30</v>
-      </c>
-      <c r="T80" t="n">
-        <v>15</v>
-      </c>
-      <c r="U80" t="n">
         <v>90</v>
       </c>
     </row>
@@ -7019,51 +6137,42 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G81" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>92</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I81" t="n">
-        <v>103</v>
+        <v>0.6796116504854369</v>
       </c>
       <c r="J81" t="n">
-        <v>0.6796116504854369</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7179487179487181</v>
       </c>
       <c r="L81" t="n">
-        <v>0.7179487179487181</v>
+        <v>0.7528089887640449</v>
       </c>
       <c r="M81" t="n">
-        <v>100</v>
+        <v>0.67</v>
       </c>
       <c r="N81" t="n">
-        <v>89</v>
+        <v>0.708994708994709</v>
       </c>
       <c r="O81" t="n">
-        <v>0.7528089887640449</v>
+        <v>70</v>
       </c>
       <c r="P81" t="n">
-        <v>0.67</v>
+        <v>22</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.708994708994709</v>
+        <v>33</v>
       </c>
       <c r="R81" t="n">
-        <v>70</v>
-      </c>
-      <c r="S81" t="n">
-        <v>22</v>
-      </c>
-      <c r="T81" t="n">
-        <v>33</v>
-      </c>
-      <c r="U81" t="n">
         <v>67</v>
       </c>
     </row>
@@ -7086,51 +6195,42 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G82" t="n">
         <v>0.765625</v>
       </c>
       <c r="H82" t="n">
-        <v>84</v>
+        <v>0.765625</v>
       </c>
       <c r="I82" t="n">
-        <v>103</v>
+        <v>0.6893203883495146</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6893203883495146</v>
+        <v>0.8452380952380952</v>
       </c>
       <c r="K82" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.7593582887700535</v>
       </c>
       <c r="L82" t="n">
-        <v>0.7593582887700535</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="M82" t="n">
-        <v>108</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="N82" t="n">
-        <v>89</v>
+        <v>0.7715736040609137</v>
       </c>
       <c r="O82" t="n">
-        <v>0.8539325842696629</v>
+        <v>71</v>
       </c>
       <c r="P82" t="n">
-        <v>0.7037037037037037</v>
+        <v>13</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.7715736040609137</v>
+        <v>32</v>
       </c>
       <c r="R82" t="n">
-        <v>71</v>
-      </c>
-      <c r="S82" t="n">
-        <v>13</v>
-      </c>
-      <c r="T82" t="n">
-        <v>32</v>
-      </c>
-      <c r="U82" t="n">
         <v>76</v>
       </c>
     </row>
@@ -7153,51 +6253,42 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G83" t="n">
         <v>0.796875</v>
       </c>
       <c r="H83" t="n">
-        <v>94</v>
+        <v>0.796875</v>
       </c>
       <c r="I83" t="n">
-        <v>103</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="J83" t="n">
-        <v>0.7669902912621359</v>
+        <v>0.8404255319148937</v>
       </c>
       <c r="K83" t="n">
-        <v>0.8404255319148937</v>
+        <v>0.8020304568527918</v>
       </c>
       <c r="L83" t="n">
-        <v>0.8020304568527918</v>
+        <v>0.8314606741573034</v>
       </c>
       <c r="M83" t="n">
-        <v>98</v>
+        <v>0.7551020408163265</v>
       </c>
       <c r="N83" t="n">
-        <v>89</v>
+        <v>0.7914438502673796</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8314606741573034</v>
+        <v>79</v>
       </c>
       <c r="P83" t="n">
-        <v>0.7551020408163265</v>
+        <v>15</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.7914438502673796</v>
+        <v>24</v>
       </c>
       <c r="R83" t="n">
-        <v>79</v>
-      </c>
-      <c r="S83" t="n">
-        <v>15</v>
-      </c>
-      <c r="T83" t="n">
-        <v>24</v>
-      </c>
-      <c r="U83" t="n">
         <v>74</v>
       </c>
     </row>
@@ -7220,51 +6311,42 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G84" t="n">
         <v>0.828125</v>
       </c>
       <c r="H84" t="n">
-        <v>103</v>
+        <v>0.828125</v>
       </c>
       <c r="I84" t="n">
-        <v>110</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8737864077669902</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8737864077669902</v>
+        <v>0.8450704225352113</v>
       </c>
       <c r="L84" t="n">
-        <v>0.8450704225352113</v>
+        <v>0.8414634146341463</v>
       </c>
       <c r="M84" t="n">
-        <v>89</v>
+        <v>0.7752808988764045</v>
       </c>
       <c r="N84" t="n">
-        <v>82</v>
+        <v>0.8070175438596492</v>
       </c>
       <c r="O84" t="n">
-        <v>0.8414634146341463</v>
+        <v>90</v>
       </c>
       <c r="P84" t="n">
-        <v>0.7752808988764045</v>
+        <v>13</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.8070175438596492</v>
+        <v>20</v>
       </c>
       <c r="R84" t="n">
-        <v>90</v>
-      </c>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>20</v>
-      </c>
-      <c r="U84" t="n">
         <v>69</v>
       </c>
     </row>
@@ -7287,51 +6369,42 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G85" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H85" t="n">
-        <v>107</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I85" t="n">
-        <v>109</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.8317757009345794</v>
       </c>
       <c r="K85" t="n">
-        <v>0.8317757009345794</v>
+        <v>0.8240740740740741</v>
       </c>
       <c r="L85" t="n">
-        <v>0.8240740740740741</v>
+        <v>0.7831325301204819</v>
       </c>
       <c r="M85" t="n">
-        <v>85</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="N85" t="n">
-        <v>83</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="O85" t="n">
-        <v>0.7831325301204819</v>
+        <v>89</v>
       </c>
       <c r="P85" t="n">
-        <v>0.7647058823529411</v>
+        <v>18</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7738095238095238</v>
+        <v>20</v>
       </c>
       <c r="R85" t="n">
-        <v>89</v>
-      </c>
-      <c r="S85" t="n">
-        <v>18</v>
-      </c>
-      <c r="T85" t="n">
-        <v>20</v>
-      </c>
-      <c r="U85" t="n">
         <v>65</v>
       </c>
     </row>
@@ -7354,51 +6427,42 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G86" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H86" t="n">
-        <v>101</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I86" t="n">
-        <v>125</v>
+        <v>0.72</v>
       </c>
       <c r="J86" t="n">
-        <v>0.72</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="L86" t="n">
-        <v>0.7964601769911505</v>
+        <v>0.835820895522388</v>
       </c>
       <c r="M86" t="n">
-        <v>91</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N86" t="n">
-        <v>67</v>
+        <v>0.7088607594936709</v>
       </c>
       <c r="O86" t="n">
-        <v>0.835820895522388</v>
+        <v>90</v>
       </c>
       <c r="P86" t="n">
-        <v>0.6153846153846154</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.7088607594936709</v>
+        <v>35</v>
       </c>
       <c r="R86" t="n">
-        <v>90</v>
-      </c>
-      <c r="S86" t="n">
-        <v>11</v>
-      </c>
-      <c r="T86" t="n">
-        <v>35</v>
-      </c>
-      <c r="U86" t="n">
         <v>56</v>
       </c>
     </row>
@@ -7421,51 +6485,42 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G87" t="n">
         <v>0.828125</v>
       </c>
       <c r="H87" t="n">
-        <v>97</v>
+        <v>0.828125</v>
       </c>
       <c r="I87" t="n">
-        <v>112</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.9072164948453608</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9072164948453608</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="L87" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.8875</v>
       </c>
       <c r="M87" t="n">
-        <v>95</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="N87" t="n">
-        <v>80</v>
+        <v>0.8114285714285715</v>
       </c>
       <c r="O87" t="n">
-        <v>0.8875</v>
+        <v>88</v>
       </c>
       <c r="P87" t="n">
-        <v>0.7473684210526316</v>
+        <v>9</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.8114285714285715</v>
+        <v>24</v>
       </c>
       <c r="R87" t="n">
-        <v>88</v>
-      </c>
-      <c r="S87" t="n">
-        <v>9</v>
-      </c>
-      <c r="T87" t="n">
-        <v>24</v>
-      </c>
-      <c r="U87" t="n">
         <v>71</v>
       </c>
     </row>
@@ -7488,51 +6543,42 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8697916666666666</v>
+        <v>167</v>
       </c>
       <c r="G88" t="n">
         <v>0.8697916666666666</v>
       </c>
       <c r="H88" t="n">
-        <v>101</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="I88" t="n">
-        <v>102</v>
+        <v>0.8725490196078431</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8725490196078431</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.8768472906403942</v>
       </c>
       <c r="L88" t="n">
-        <v>0.8768472906403942</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="M88" t="n">
-        <v>91</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N88" t="n">
-        <v>90</v>
+        <v>0.8618784530386741</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8666666666666667</v>
+        <v>89</v>
       </c>
       <c r="P88" t="n">
-        <v>0.8571428571428571</v>
+        <v>12</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.8618784530386741</v>
+        <v>13</v>
       </c>
       <c r="R88" t="n">
-        <v>89</v>
-      </c>
-      <c r="S88" t="n">
-        <v>12</v>
-      </c>
-      <c r="T88" t="n">
-        <v>13</v>
-      </c>
-      <c r="U88" t="n">
         <v>78</v>
       </c>
     </row>
@@ -7555,51 +6601,42 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G89" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H89" t="n">
-        <v>103</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I89" t="n">
-        <v>125</v>
+        <v>0.752</v>
       </c>
       <c r="J89" t="n">
-        <v>0.752</v>
+        <v>0.912621359223301</v>
       </c>
       <c r="K89" t="n">
-        <v>0.912621359223301</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="L89" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8656716417910447</v>
       </c>
       <c r="M89" t="n">
-        <v>89</v>
+        <v>0.651685393258427</v>
       </c>
       <c r="N89" t="n">
-        <v>67</v>
+        <v>0.7435897435897435</v>
       </c>
       <c r="O89" t="n">
-        <v>0.8656716417910447</v>
+        <v>94</v>
       </c>
       <c r="P89" t="n">
-        <v>0.651685393258427</v>
+        <v>9</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.7435897435897435</v>
+        <v>31</v>
       </c>
       <c r="R89" t="n">
-        <v>94</v>
-      </c>
-      <c r="S89" t="n">
-        <v>9</v>
-      </c>
-      <c r="T89" t="n">
-        <v>31</v>
-      </c>
-      <c r="U89" t="n">
         <v>58</v>
       </c>
     </row>
@@ -7622,51 +6659,42 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G90" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>100</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I90" t="n">
-        <v>89</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="J90" t="n">
-        <v>0.8539325842696629</v>
+        <v>0.76</v>
       </c>
       <c r="K90" t="n">
-        <v>0.76</v>
+        <v>0.8042328042328041</v>
       </c>
       <c r="L90" t="n">
-        <v>0.8042328042328041</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="M90" t="n">
-        <v>92</v>
+        <v>0.8586956521739131</v>
       </c>
       <c r="N90" t="n">
-        <v>103</v>
+        <v>0.8102564102564102</v>
       </c>
       <c r="O90" t="n">
-        <v>0.7669902912621359</v>
+        <v>76</v>
       </c>
       <c r="P90" t="n">
-        <v>0.8586956521739131</v>
+        <v>24</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.8102564102564102</v>
+        <v>13</v>
       </c>
       <c r="R90" t="n">
-        <v>76</v>
-      </c>
-      <c r="S90" t="n">
-        <v>24</v>
-      </c>
-      <c r="T90" t="n">
-        <v>13</v>
-      </c>
-      <c r="U90" t="n">
         <v>79</v>
       </c>
     </row>
@@ -7689,51 +6717,42 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G91" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H91" t="n">
-        <v>105</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I91" t="n">
-        <v>114</v>
+        <v>0.7456140350877193</v>
       </c>
       <c r="J91" t="n">
-        <v>0.7456140350877193</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="K91" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.776255707762557</v>
       </c>
       <c r="L91" t="n">
-        <v>0.776255707762557</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="M91" t="n">
-        <v>87</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N91" t="n">
-        <v>78</v>
+        <v>0.7030303030303031</v>
       </c>
       <c r="O91" t="n">
-        <v>0.7435897435897436</v>
+        <v>85</v>
       </c>
       <c r="P91" t="n">
-        <v>0.6666666666666666</v>
+        <v>20</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.7030303030303031</v>
+        <v>29</v>
       </c>
       <c r="R91" t="n">
-        <v>85</v>
-      </c>
-      <c r="S91" t="n">
-        <v>20</v>
-      </c>
-      <c r="T91" t="n">
-        <v>29</v>
-      </c>
-      <c r="U91" t="n">
         <v>58</v>
       </c>
     </row>
@@ -7756,51 +6775,42 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G92" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>106</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I92" t="n">
-        <v>105</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8207547169811321</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8207547169811321</v>
+        <v>0.8246445497630333</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8246445497630333</v>
+        <v>0.7816091954022989</v>
       </c>
       <c r="M92" t="n">
-        <v>86</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="N92" t="n">
+        <v>0.7861271676300577</v>
+      </c>
+      <c r="O92" t="n">
         <v>87</v>
       </c>
-      <c r="O92" t="n">
-        <v>0.7816091954022989</v>
-      </c>
       <c r="P92" t="n">
-        <v>0.7906976744186046</v>
+        <v>19</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.7861271676300577</v>
+        <v>18</v>
       </c>
       <c r="R92" t="n">
-        <v>87</v>
-      </c>
-      <c r="S92" t="n">
-        <v>19</v>
-      </c>
-      <c r="T92" t="n">
-        <v>18</v>
-      </c>
-      <c r="U92" t="n">
         <v>68</v>
       </c>
     </row>
@@ -7823,51 +6833,42 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8385416666666666</v>
+        <v>161</v>
       </c>
       <c r="G93" t="n">
         <v>0.8385416666666666</v>
       </c>
       <c r="H93" t="n">
-        <v>103</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I93" t="n">
-        <v>96</v>
+        <v>0.875</v>
       </c>
       <c r="J93" t="n">
-        <v>0.875</v>
+        <v>0.8155339805825242</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8155339805825242</v>
+        <v>0.8442211055276382</v>
       </c>
       <c r="L93" t="n">
-        <v>0.8442211055276382</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="M93" t="n">
-        <v>89</v>
+        <v>0.8651685393258427</v>
       </c>
       <c r="N93" t="n">
-        <v>96</v>
+        <v>0.8324324324324325</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8020833333333334</v>
+        <v>84</v>
       </c>
       <c r="P93" t="n">
-        <v>0.8651685393258427</v>
+        <v>19</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.8324324324324325</v>
+        <v>12</v>
       </c>
       <c r="R93" t="n">
-        <v>84</v>
-      </c>
-      <c r="S93" t="n">
-        <v>19</v>
-      </c>
-      <c r="T93" t="n">
-        <v>12</v>
-      </c>
-      <c r="U93" t="n">
         <v>77</v>
       </c>
     </row>
@@ -7890,51 +6891,42 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G94" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H94" t="n">
-        <v>104</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I94" t="n">
-        <v>124</v>
+        <v>0.7338709677419355</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7338709677419355</v>
+        <v>0.875</v>
       </c>
       <c r="K94" t="n">
-        <v>0.875</v>
+        <v>0.7982456140350876</v>
       </c>
       <c r="L94" t="n">
-        <v>0.7982456140350876</v>
+        <v>0.8088235294117647</v>
       </c>
       <c r="M94" t="n">
-        <v>88</v>
+        <v>0.625</v>
       </c>
       <c r="N94" t="n">
-        <v>68</v>
+        <v>0.7051282051282051</v>
       </c>
       <c r="O94" t="n">
-        <v>0.8088235294117647</v>
+        <v>91</v>
       </c>
       <c r="P94" t="n">
-        <v>0.625</v>
+        <v>13</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.7051282051282051</v>
+        <v>33</v>
       </c>
       <c r="R94" t="n">
-        <v>91</v>
-      </c>
-      <c r="S94" t="n">
-        <v>13</v>
-      </c>
-      <c r="T94" t="n">
-        <v>33</v>
-      </c>
-      <c r="U94" t="n">
         <v>55</v>
       </c>
     </row>
@@ -7957,51 +6949,42 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.828125</v>
+        <v>159</v>
       </c>
       <c r="G95" t="n">
         <v>0.828125</v>
       </c>
       <c r="H95" t="n">
-        <v>96</v>
+        <v>0.828125</v>
       </c>
       <c r="I95" t="n">
-        <v>77</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L95" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7739130434782608</v>
       </c>
       <c r="M95" t="n">
-        <v>96</v>
+        <v>0.9270833333333334</v>
       </c>
       <c r="N95" t="n">
-        <v>115</v>
+        <v>0.8436018957345971</v>
       </c>
       <c r="O95" t="n">
-        <v>0.7739130434782608</v>
+        <v>70</v>
       </c>
       <c r="P95" t="n">
-        <v>0.9270833333333334</v>
+        <v>26</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.8436018957345971</v>
+        <v>7</v>
       </c>
       <c r="R95" t="n">
-        <v>70</v>
-      </c>
-      <c r="S95" t="n">
-        <v>26</v>
-      </c>
-      <c r="T95" t="n">
-        <v>7</v>
-      </c>
-      <c r="U95" t="n">
         <v>89</v>
       </c>
     </row>
@@ -8024,51 +7007,42 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.859375</v>
+        <v>165</v>
       </c>
       <c r="G96" t="n">
         <v>0.859375</v>
       </c>
       <c r="H96" t="n">
-        <v>94</v>
+        <v>0.859375</v>
       </c>
       <c r="I96" t="n">
-        <v>103</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.9042553191489362</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9042553191489362</v>
+        <v>0.8629441624365481</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8629441624365481</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="M96" t="n">
-        <v>98</v>
+        <v>0.8163265306122449</v>
       </c>
       <c r="N96" t="n">
-        <v>89</v>
+        <v>0.8556149732620321</v>
       </c>
       <c r="O96" t="n">
-        <v>0.898876404494382</v>
+        <v>85</v>
       </c>
       <c r="P96" t="n">
-        <v>0.8163265306122449</v>
+        <v>9</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.8556149732620321</v>
+        <v>18</v>
       </c>
       <c r="R96" t="n">
-        <v>85</v>
-      </c>
-      <c r="S96" t="n">
-        <v>9</v>
-      </c>
-      <c r="T96" t="n">
-        <v>18</v>
-      </c>
-      <c r="U96" t="n">
         <v>80</v>
       </c>
     </row>
@@ -8091,51 +7065,42 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G97" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H97" t="n">
-        <v>94</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I97" t="n">
-        <v>88</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="J97" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.8131868131868133</v>
       </c>
       <c r="L97" t="n">
-        <v>0.8131868131868133</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="M97" t="n">
-        <v>98</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N97" t="n">
-        <v>104</v>
+        <v>0.8316831683168318</v>
       </c>
       <c r="O97" t="n">
-        <v>0.8076923076923077</v>
+        <v>74</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8571428571428571</v>
+        <v>20</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.8316831683168318</v>
+        <v>14</v>
       </c>
       <c r="R97" t="n">
-        <v>74</v>
-      </c>
-      <c r="S97" t="n">
-        <v>20</v>
-      </c>
-      <c r="T97" t="n">
-        <v>14</v>
-      </c>
-      <c r="U97" t="n">
         <v>84</v>
       </c>
     </row>
@@ -8158,51 +7123,42 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.859375</v>
+        <v>165</v>
       </c>
       <c r="G98" t="n">
         <v>0.859375</v>
       </c>
       <c r="H98" t="n">
-        <v>90</v>
+        <v>0.859375</v>
       </c>
       <c r="I98" t="n">
-        <v>97</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K98" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8556149732620321</v>
       </c>
       <c r="L98" t="n">
-        <v>0.8556149732620321</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="M98" t="n">
-        <v>102</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N98" t="n">
-        <v>95</v>
+        <v>0.8629441624365481</v>
       </c>
       <c r="O98" t="n">
-        <v>0.8947368421052632</v>
+        <v>80</v>
       </c>
       <c r="P98" t="n">
-        <v>0.8333333333333334</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.8629441624365481</v>
+        <v>17</v>
       </c>
       <c r="R98" t="n">
-        <v>80</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="n">
-        <v>17</v>
-      </c>
-      <c r="U98" t="n">
         <v>85</v>
       </c>
     </row>
@@ -8225,51 +7181,42 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G99" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H99" t="n">
-        <v>101</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I99" t="n">
-        <v>106</v>
+        <v>0.8018867924528302</v>
       </c>
       <c r="J99" t="n">
-        <v>0.8018867924528302</v>
+        <v>0.8415841584158416</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.821256038647343</v>
       </c>
       <c r="L99" t="n">
-        <v>0.821256038647343</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="M99" t="n">
-        <v>91</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="N99" t="n">
-        <v>86</v>
+        <v>0.7909604519774011</v>
       </c>
       <c r="O99" t="n">
-        <v>0.813953488372093</v>
+        <v>85</v>
       </c>
       <c r="P99" t="n">
-        <v>0.7692307692307693</v>
+        <v>16</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.7909604519774011</v>
+        <v>21</v>
       </c>
       <c r="R99" t="n">
-        <v>85</v>
-      </c>
-      <c r="S99" t="n">
-        <v>16</v>
-      </c>
-      <c r="T99" t="n">
-        <v>21</v>
-      </c>
-      <c r="U99" t="n">
         <v>70</v>
       </c>
     </row>
@@ -8292,51 +7239,42 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G100" t="n">
         <v>0.796875</v>
       </c>
       <c r="H100" t="n">
-        <v>90</v>
+        <v>0.796875</v>
       </c>
       <c r="I100" t="n">
-        <v>101</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="K100" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.7958115183246073</v>
       </c>
       <c r="L100" t="n">
-        <v>0.7958115183246073</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M100" t="n">
-        <v>102</v>
+        <v>0.7549019607843137</v>
       </c>
       <c r="N100" t="n">
-        <v>91</v>
+        <v>0.7979274611398963</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8461538461538461</v>
+        <v>76</v>
       </c>
       <c r="P100" t="n">
-        <v>0.7549019607843137</v>
+        <v>14</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.7979274611398963</v>
+        <v>25</v>
       </c>
       <c r="R100" t="n">
-        <v>76</v>
-      </c>
-      <c r="S100" t="n">
-        <v>14</v>
-      </c>
-      <c r="T100" t="n">
-        <v>25</v>
-      </c>
-      <c r="U100" t="n">
         <v>77</v>
       </c>
     </row>
@@ -8359,51 +7297,42 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6927083333333334</v>
+        <v>133</v>
       </c>
       <c r="G101" t="n">
         <v>0.6927083333333334</v>
       </c>
       <c r="H101" t="n">
-        <v>98</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="I101" t="n">
-        <v>131</v>
+        <v>0.648854961832061</v>
       </c>
       <c r="J101" t="n">
-        <v>0.648854961832061</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="K101" t="n">
-        <v>0.8673469387755102</v>
+        <v>0.74235807860262</v>
       </c>
       <c r="L101" t="n">
-        <v>0.74235807860262</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="M101" t="n">
-        <v>94</v>
+        <v>0.5106382978723404</v>
       </c>
       <c r="N101" t="n">
-        <v>61</v>
+        <v>0.6193548387096774</v>
       </c>
       <c r="O101" t="n">
-        <v>0.7868852459016393</v>
+        <v>85</v>
       </c>
       <c r="P101" t="n">
-        <v>0.5106382978723404</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.6193548387096774</v>
+        <v>46</v>
       </c>
       <c r="R101" t="n">
-        <v>85</v>
-      </c>
-      <c r="S101" t="n">
-        <v>13</v>
-      </c>
-      <c r="T101" t="n">
-        <v>46</v>
-      </c>
-      <c r="U101" t="n">
         <v>48</v>
       </c>
     </row>
@@ -8424,19 +7353,19 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>predicted_0</t>
+          <t>pred_0</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>predicted_1</t>
+          <t>pred_1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>actual_0</t>
+          <t>true_0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8449,7 +7378,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>actual_1</t>
+          <t>true_1</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -8481,22 +7410,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>actual_0_pred_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>actual_1_pred_0</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
